--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBB39FB-859D-4787-8CDD-703F9731F2CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DDA4D6-A2FA-4DB9-A057-9A7BBBE17824}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$154</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$586</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$586</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$153</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$585</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$585</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="223">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1001,6 +1001,9 @@
   </si>
   <si>
     <t>ХОЧУ ВЕТЧ. МРАМОР. с/н мгс 1/100_45с_Л11</t>
+  </si>
+  <si>
+    <t>ДОМАШНИЙ РЕЦЕПТ Коровино вар п/о_332к</t>
   </si>
 </sst>
 </file>
@@ -9209,7 +9212,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1674"/>
+  <dimension ref="A1:BO1673"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -9538,7 +9541,7 @@
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="134" t="str">
-        <f t="shared" ref="A12:A72" si="1">RIGHT(D12,4)</f>
+        <f t="shared" ref="A12:A71" si="1">RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
       <c r="B12" s="51" t="s">
@@ -9800,28 +9803,24 @@
     <row r="15" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6861</v>
+        <v>7754</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="50">
-        <v>1001015646861</v>
+        <v>1001015647754</v>
       </c>
       <c r="E15" s="24"/>
-      <c r="F15" s="23">
-        <v>1.95</v>
-      </c>
+      <c r="F15" s="23"/>
       <c r="G15" s="23">
         <f>E15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="14">
-        <v>3.9</v>
-      </c>
+      <c r="H15" s="14"/>
       <c r="I15" s="14">
         <v>60</v>
       </c>
@@ -9869,27 +9868,27 @@
     <row r="16" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6862</v>
+        <v>6498</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C16" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="50">
-        <v>1001015706862</v>
+        <v>1001012456498</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="23">
-        <v>1.95</v>
+        <v>1</v>
       </c>
       <c r="G16" s="23">
-        <f t="shared" ref="G16:G18" si="2">E16</f>
+        <f t="shared" ref="G16:G17" si="2">E16</f>
         <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I16" s="14">
         <v>60</v>
@@ -9900,27 +9899,27 @@
     <row r="17" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6498</v>
+        <v>4063</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C17" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="50">
-        <v>1001012456498</v>
+        <v>1001012484063</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="23">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="G17" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="I17" s="14">
         <v>60</v>
@@ -9931,27 +9930,27 @@
     <row r="18" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>4063</v>
+        <v>6333</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="50">
-        <v>1001012484063</v>
+        <v>1001012486333</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="23">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G18" s="23">
-        <f t="shared" si="2"/>
+        <f>E18*F18</f>
         <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I18" s="14">
         <v>60</v>
@@ -9962,27 +9961,27 @@
     <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6333</v>
+        <v>4574</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="50">
-        <v>1001012486333</v>
+        <v>1001012634574</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="23">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G19" s="23">
-        <f>E19*F19</f>
+        <f>E19</f>
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I19" s="14">
         <v>60</v>
@@ -9993,27 +9992,27 @@
     <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>4574</v>
+        <v>7334</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" s="50">
-        <v>1001012634574</v>
+        <v>1001012637334</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="23">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G20" s="23">
-        <f>E20</f>
+        <f>E20*F20</f>
         <v>0</v>
       </c>
       <c r="H20" s="14">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I20" s="14">
         <v>60</v>
@@ -10021,61 +10020,117 @@
       <c r="J20" s="29"/>
       <c r="L20" s="100"/>
     </row>
-    <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7334</v>
+        <v>4813</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="50">
-        <v>1001012637334</v>
+        <v>1001012564813</v>
       </c>
       <c r="E21" s="24"/>
-      <c r="F21" s="23">
-        <v>0.4</v>
+      <c r="F21" s="125">
+        <v>1.35</v>
       </c>
       <c r="G21" s="23">
-        <f>E21*F21</f>
+        <f>E21</f>
         <v>0</v>
       </c>
-      <c r="H21" s="14">
-        <v>3.2</v>
-      </c>
-      <c r="I21" s="14">
+      <c r="H21" s="29">
+        <v>4.05</v>
+      </c>
+      <c r="I21" s="29">
         <v>60</v>
       </c>
       <c r="J21" s="29"/>
+      <c r="K21" s="27"/>
       <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="100"/>
+      <c r="S21" s="100"/>
+      <c r="T21" s="100"/>
+      <c r="U21" s="100"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="100"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="100"/>
+      <c r="Z21" s="100"/>
+      <c r="AA21" s="100"/>
+      <c r="AB21" s="100"/>
+      <c r="AC21" s="100"/>
+      <c r="AD21" s="100"/>
+      <c r="AE21" s="100"/>
+      <c r="AF21" s="100"/>
+      <c r="AG21" s="100"/>
+      <c r="AH21" s="100"/>
+      <c r="AI21" s="100"/>
+      <c r="AJ21" s="100"/>
+      <c r="AK21" s="100"/>
+      <c r="AL21" s="100"/>
+      <c r="AM21" s="100"/>
+      <c r="AN21" s="100"/>
+      <c r="AO21" s="100"/>
+      <c r="AP21" s="100"/>
+      <c r="AQ21" s="100"/>
+      <c r="AR21" s="100"/>
+      <c r="AS21" s="100"/>
+      <c r="AT21" s="100"/>
+      <c r="AU21" s="100"/>
+      <c r="AV21" s="100"/>
+      <c r="AW21" s="100"/>
+      <c r="AX21" s="100"/>
+      <c r="AY21" s="100"/>
+      <c r="AZ21" s="100"/>
+      <c r="BA21" s="100"/>
+      <c r="BB21" s="100"/>
+      <c r="BC21" s="100"/>
+      <c r="BD21" s="100"/>
+      <c r="BE21" s="100"/>
+      <c r="BF21" s="100"/>
+      <c r="BG21" s="100"/>
+      <c r="BH21" s="100"/>
+      <c r="BI21" s="100"/>
+      <c r="BJ21" s="100"/>
+      <c r="BK21" s="100"/>
+      <c r="BL21" s="100"/>
+      <c r="BM21" s="100"/>
+      <c r="BN21" s="100"/>
+      <c r="BO21" s="100"/>
     </row>
     <row r="22" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>4813</v>
+        <v>6392</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D22" s="50">
-        <v>1001012564813</v>
+        <v>1001012566392</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="125">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G22" s="23">
-        <f>E22</f>
+        <f>E22*F22</f>
         <v>0</v>
       </c>
       <c r="H22" s="29">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I22" s="29">
         <v>60</v>
@@ -10142,27 +10197,27 @@
     <row r="23" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6392</v>
+        <v>5851</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D23" s="50">
-        <v>1001012566392</v>
+        <v>1001012505851</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="125">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G23" s="23">
-        <f>E23*F23</f>
+        <f>E23</f>
         <v>0</v>
       </c>
       <c r="H23" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I23" s="29">
         <v>60</v>
@@ -10226,119 +10281,63 @@
       <c r="BN23" s="100"/>
       <c r="BO23" s="100"/>
     </row>
-    <row r="24" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>5851</v>
+        <v>7632</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" s="50">
-        <v>1001012505851</v>
+        <v>1001012507632</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="125">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G24" s="23">
-        <f>E24</f>
+        <f>E24*F24</f>
         <v>0</v>
       </c>
       <c r="H24" s="29">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I24" s="29">
         <v>60</v>
       </c>
       <c r="J24" s="29"/>
-      <c r="K24" s="27"/>
       <c r="L24" s="100"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="100"/>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="100"/>
-      <c r="T24" s="100"/>
-      <c r="U24" s="100"/>
-      <c r="V24" s="100"/>
-      <c r="W24" s="100"/>
-      <c r="X24" s="100"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="100"/>
-      <c r="AA24" s="100"/>
-      <c r="AB24" s="100"/>
-      <c r="AC24" s="100"/>
-      <c r="AD24" s="100"/>
-      <c r="AE24" s="100"/>
-      <c r="AF24" s="100"/>
-      <c r="AG24" s="100"/>
-      <c r="AH24" s="100"/>
-      <c r="AI24" s="100"/>
-      <c r="AJ24" s="100"/>
-      <c r="AK24" s="100"/>
-      <c r="AL24" s="100"/>
-      <c r="AM24" s="100"/>
-      <c r="AN24" s="100"/>
-      <c r="AO24" s="100"/>
-      <c r="AP24" s="100"/>
-      <c r="AQ24" s="100"/>
-      <c r="AR24" s="100"/>
-      <c r="AS24" s="100"/>
-      <c r="AT24" s="100"/>
-      <c r="AU24" s="100"/>
-      <c r="AV24" s="100"/>
-      <c r="AW24" s="100"/>
-      <c r="AX24" s="100"/>
-      <c r="AY24" s="100"/>
-      <c r="AZ24" s="100"/>
-      <c r="BA24" s="100"/>
-      <c r="BB24" s="100"/>
-      <c r="BC24" s="100"/>
-      <c r="BD24" s="100"/>
-      <c r="BE24" s="100"/>
-      <c r="BF24" s="100"/>
-      <c r="BG24" s="100"/>
-      <c r="BH24" s="100"/>
-      <c r="BI24" s="100"/>
-      <c r="BJ24" s="100"/>
-      <c r="BK24" s="100"/>
-      <c r="BL24" s="100"/>
-      <c r="BM24" s="100"/>
-      <c r="BN24" s="100"/>
-      <c r="BO24" s="100"/>
     </row>
     <row r="25" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7632</v>
+        <v>4561</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>188</v>
+        <v>111</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D25" s="50">
-        <v>1001012507632</v>
+        <v>1001010014561</v>
       </c>
       <c r="E25" s="24"/>
-      <c r="F25" s="125">
-        <v>0.4</v>
+      <c r="F25" s="23">
+        <v>1.35</v>
       </c>
       <c r="G25" s="23">
-        <f>E25*F25</f>
+        <f t="shared" ref="G25" si="3">E25</f>
         <v>0</v>
       </c>
-      <c r="H25" s="29">
-        <v>3.2</v>
-      </c>
-      <c r="I25" s="29">
+      <c r="H25" s="14">
+        <v>4.05</v>
+      </c>
+      <c r="I25" s="14">
         <v>60</v>
       </c>
       <c r="J25" s="29"/>
@@ -10347,27 +10346,27 @@
     <row r="26" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>4561</v>
+        <v>6325</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D26" s="50">
-        <v>1001010014561</v>
+        <v>1001010106325</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="23">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="23">
-        <f t="shared" ref="G26" si="3">E26</f>
+        <f>E26*F26</f>
         <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I26" s="14">
         <v>60</v>
@@ -10375,66 +10374,119 @@
       <c r="J26" s="29"/>
       <c r="L26" s="100"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6325</v>
+        <v>8014</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D27" s="50">
-        <v>1001010106325</v>
+        <v>1001010108014</v>
       </c>
       <c r="E27" s="24"/>
-      <c r="F27" s="23">
-        <v>0.4</v>
+      <c r="F27" s="125">
+        <v>1.35</v>
       </c>
       <c r="G27" s="23">
-        <f>E27*F27</f>
+        <f t="shared" ref="G27" si="4">E27</f>
         <v>0</v>
       </c>
-      <c r="H27" s="14">
-        <v>3.2</v>
-      </c>
-      <c r="I27" s="14">
+      <c r="H27" s="29">
+        <v>5.4</v>
+      </c>
+      <c r="I27" s="29">
         <v>60</v>
       </c>
       <c r="J27" s="29"/>
+      <c r="K27" s="27"/>
       <c r="L27" s="100"/>
+      <c r="M27" s="100"/>
+      <c r="N27" s="100"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="100"/>
+      <c r="Q27" s="100"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="100"/>
+      <c r="T27" s="100"/>
+      <c r="U27" s="100"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="100"/>
+      <c r="X27" s="100"/>
+      <c r="Y27" s="100"/>
+      <c r="Z27" s="100"/>
+      <c r="AA27" s="100"/>
+      <c r="AB27" s="100"/>
+      <c r="AC27" s="100"/>
+      <c r="AD27" s="100"/>
+      <c r="AE27" s="100"/>
+      <c r="AF27" s="100"/>
+      <c r="AG27" s="100"/>
+      <c r="AH27" s="100"/>
+      <c r="AI27" s="100"/>
+      <c r="AJ27" s="100"/>
+      <c r="AK27" s="100"/>
+      <c r="AL27" s="100"/>
+      <c r="AM27" s="100"/>
+      <c r="AN27" s="100"/>
+      <c r="AO27" s="100"/>
+      <c r="AP27" s="100"/>
+      <c r="AQ27" s="100"/>
+      <c r="AR27" s="100"/>
+      <c r="AS27" s="100"/>
+      <c r="AT27" s="100"/>
+      <c r="AU27" s="100"/>
+      <c r="AV27" s="100"/>
+      <c r="AW27" s="100"/>
+      <c r="AX27" s="100"/>
+      <c r="AY27" s="100"/>
+      <c r="AZ27" s="100"/>
+      <c r="BA27" s="100"/>
+      <c r="BB27" s="100"/>
+      <c r="BC27" s="100"/>
+      <c r="BD27" s="100"/>
+      <c r="BE27" s="100"/>
+      <c r="BF27" s="100"/>
+      <c r="BG27" s="100"/>
+      <c r="BH27" s="100"/>
+      <c r="BI27" s="100"/>
+      <c r="BJ27" s="100"/>
+      <c r="BK27" s="100"/>
+      <c r="BL27" s="100"/>
+      <c r="BM27" s="100"/>
+      <c r="BN27" s="100"/>
+      <c r="BO27" s="100"/>
     </row>
     <row r="28" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>8014</v>
+        <v>7514</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D28" s="50">
-        <v>1001010108014</v>
+        <v>1001017557514</v>
       </c>
       <c r="E28" s="24"/>
-      <c r="F28" s="125">
-        <v>1.35</v>
-      </c>
+      <c r="F28" s="125"/>
       <c r="G28" s="23">
-        <f t="shared" ref="G28" si="4">E28</f>
+        <f>E28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="29">
-        <v>5.4</v>
-      </c>
-      <c r="I28" s="29">
-        <v>60</v>
-      </c>
-      <c r="J28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29" t="str">
+        <f>VLOOKUP(D28,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="K28" s="27"/>
       <c r="L28" s="100"/>
       <c r="M28" s="100"/>
@@ -10496,16 +10548,16 @@
     <row r="29" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7514</v>
+        <v>7518</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D29" s="50">
-        <v>1001017557514</v>
+        <v>1001017567518</v>
       </c>
       <c r="E29" s="24"/>
       <c r="F29" s="125"/>
@@ -10580,29 +10632,32 @@
     <row r="30" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7518</v>
+        <v>7343</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D30" s="50">
-        <v>1001017567518</v>
+        <v>1001016747343</v>
       </c>
       <c r="E30" s="24"/>
-      <c r="F30" s="125"/>
+      <c r="F30" s="125">
+        <v>0.4</v>
+      </c>
       <c r="G30" s="23">
-        <f>E30</f>
+        <f t="shared" ref="G30:G32" si="5">E30*F30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29" t="str">
-        <f>VLOOKUP(D30,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H30" s="29">
+        <v>3.2</v>
+      </c>
+      <c r="I30" s="29">
+        <v>60</v>
+      </c>
+      <c r="J30" s="29"/>
       <c r="K30" s="27"/>
       <c r="L30" s="100"/>
       <c r="M30" s="100"/>
@@ -10661,26 +10716,26 @@
       <c r="BN30" s="100"/>
       <c r="BO30" s="100"/>
     </row>
-    <row r="31" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7343</v>
+        <v>6797</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="C31" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="50">
-        <v>1001016747343</v>
+        <v>1001015026797</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="125">
         <v>0.4</v>
       </c>
       <c r="G31" s="23">
-        <f t="shared" ref="G31:G33" si="5">E31*F31</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H31" s="29">
@@ -10690,124 +10745,110 @@
         <v>60</v>
       </c>
       <c r="J31" s="29"/>
-      <c r="K31" s="27"/>
       <c r="L31" s="100"/>
-      <c r="M31" s="100"/>
-      <c r="N31" s="100"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="100"/>
-      <c r="Q31" s="100"/>
-      <c r="R31" s="100"/>
-      <c r="S31" s="100"/>
-      <c r="T31" s="100"/>
-      <c r="U31" s="100"/>
-      <c r="V31" s="100"/>
-      <c r="W31" s="100"/>
-      <c r="X31" s="100"/>
-      <c r="Y31" s="100"/>
-      <c r="Z31" s="100"/>
-      <c r="AA31" s="100"/>
-      <c r="AB31" s="100"/>
-      <c r="AC31" s="100"/>
-      <c r="AD31" s="100"/>
-      <c r="AE31" s="100"/>
-      <c r="AF31" s="100"/>
-      <c r="AG31" s="100"/>
-      <c r="AH31" s="100"/>
-      <c r="AI31" s="100"/>
-      <c r="AJ31" s="100"/>
-      <c r="AK31" s="100"/>
-      <c r="AL31" s="100"/>
-      <c r="AM31" s="100"/>
-      <c r="AN31" s="100"/>
-      <c r="AO31" s="100"/>
-      <c r="AP31" s="100"/>
-      <c r="AQ31" s="100"/>
-      <c r="AR31" s="100"/>
-      <c r="AS31" s="100"/>
-      <c r="AT31" s="100"/>
-      <c r="AU31" s="100"/>
-      <c r="AV31" s="100"/>
-      <c r="AW31" s="100"/>
-      <c r="AX31" s="100"/>
-      <c r="AY31" s="100"/>
-      <c r="AZ31" s="100"/>
-      <c r="BA31" s="100"/>
-      <c r="BB31" s="100"/>
-      <c r="BC31" s="100"/>
-      <c r="BD31" s="100"/>
-      <c r="BE31" s="100"/>
-      <c r="BF31" s="100"/>
-      <c r="BG31" s="100"/>
-      <c r="BH31" s="100"/>
-      <c r="BI31" s="100"/>
-      <c r="BJ31" s="100"/>
-      <c r="BK31" s="100"/>
-      <c r="BL31" s="100"/>
-      <c r="BM31" s="100"/>
-      <c r="BN31" s="100"/>
-      <c r="BO31" s="100"/>
-    </row>
-    <row r="32" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6797</v>
+        <v>7231</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="C32" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="50">
-        <v>1001015026797</v>
+        <v>1001013957231</v>
       </c>
       <c r="E32" s="24"/>
       <c r="F32" s="125">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G32" s="23">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H32" s="29">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I32" s="29">
         <v>60</v>
       </c>
       <c r="J32" s="29"/>
+      <c r="K32" s="27"/>
       <c r="L32" s="100"/>
-    </row>
-    <row r="33" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="134" t="str">
-        <f t="shared" si="1"/>
-        <v>7231</v>
-      </c>
-      <c r="B33" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="50">
-        <v>1001013957231</v>
-      </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="125">
-        <v>0.3</v>
-      </c>
-      <c r="G33" s="23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="29">
-        <v>2.4</v>
-      </c>
-      <c r="I33" s="29">
-        <v>60</v>
-      </c>
-      <c r="J33" s="29"/>
+      <c r="M32" s="100"/>
+      <c r="N32" s="100"/>
+      <c r="O32" s="100"/>
+      <c r="P32" s="100"/>
+      <c r="Q32" s="100"/>
+      <c r="R32" s="100"/>
+      <c r="S32" s="100"/>
+      <c r="T32" s="100"/>
+      <c r="U32" s="100"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="100"/>
+      <c r="X32" s="100"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="100"/>
+      <c r="AC32" s="100"/>
+      <c r="AD32" s="100"/>
+      <c r="AE32" s="100"/>
+      <c r="AF32" s="100"/>
+      <c r="AG32" s="100"/>
+      <c r="AH32" s="100"/>
+      <c r="AI32" s="100"/>
+      <c r="AJ32" s="100"/>
+      <c r="AK32" s="100"/>
+      <c r="AL32" s="100"/>
+      <c r="AM32" s="100"/>
+      <c r="AN32" s="100"/>
+      <c r="AO32" s="100"/>
+      <c r="AP32" s="100"/>
+      <c r="AQ32" s="100"/>
+      <c r="AR32" s="100"/>
+      <c r="AS32" s="100"/>
+      <c r="AT32" s="100"/>
+      <c r="AU32" s="100"/>
+      <c r="AV32" s="100"/>
+      <c r="AW32" s="100"/>
+      <c r="AX32" s="100"/>
+      <c r="AY32" s="100"/>
+      <c r="AZ32" s="100"/>
+      <c r="BA32" s="100"/>
+      <c r="BB32" s="100"/>
+      <c r="BC32" s="100"/>
+      <c r="BD32" s="100"/>
+      <c r="BE32" s="100"/>
+      <c r="BF32" s="100"/>
+      <c r="BG32" s="100"/>
+      <c r="BH32" s="100"/>
+      <c r="BI32" s="100"/>
+      <c r="BJ32" s="100"/>
+      <c r="BK32" s="100"/>
+      <c r="BL32" s="100"/>
+      <c r="BM32" s="100"/>
+      <c r="BN32" s="100"/>
+      <c r="BO32" s="100"/>
+    </row>
+    <row r="33" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="43"/>
       <c r="K33" s="27"/>
       <c r="L33" s="100"/>
       <c r="M33" s="100"/>
@@ -10866,21 +10907,35 @@
       <c r="BN33" s="100"/>
       <c r="BO33" s="100"/>
     </row>
-    <row r="34" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="43"/>
+    <row r="34" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="134" t="str">
+        <f t="shared" si="1"/>
+        <v>6602</v>
+      </c>
+      <c r="B34" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="50">
+        <v>1001021966602</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="125">
+        <v>0.35</v>
+      </c>
+      <c r="G34" s="23">
+        <f t="shared" ref="G34:G38" si="6">E34*F34</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="29">
+        <v>2.8</v>
+      </c>
+      <c r="I34" s="29">
+        <v>45</v>
+      </c>
+      <c r="J34" s="29"/>
       <c r="K34" s="27"/>
       <c r="L34" s="100"/>
       <c r="M34" s="100"/>
@@ -10939,33 +10994,33 @@
       <c r="BN34" s="100"/>
       <c r="BO34" s="100"/>
     </row>
-    <row r="35" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6602</v>
+        <v>7601</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>155</v>
+        <v>201</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="50">
-        <v>1001021966602</v>
+        <v>1001025767601</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="125">
-        <v>0.35</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" ref="G35:G39" si="6">E35*F35</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="29">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="I35" s="29">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J35" s="29"/>
       <c r="K35" s="27"/>
@@ -11029,27 +11084,27 @@
     <row r="36" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7601</v>
+        <v>7461</v>
       </c>
       <c r="B36" s="51" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C36" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="50">
-        <v>1001025767601</v>
+        <v>1001025767461</v>
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="125">
-        <v>0.26400000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="G36" s="23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="29">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="I36" s="29">
         <v>30</v>
@@ -11116,31 +11171,27 @@
     <row r="37" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7461</v>
+        <v>7040</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C37" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="50">
-        <v>1001025767461</v>
+        <v>1001025027040</v>
       </c>
       <c r="E37" s="24"/>
       <c r="F37" s="125">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="G37" s="23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H37" s="29">
-        <v>1.98</v>
-      </c>
-      <c r="I37" s="29">
-        <v>30</v>
-      </c>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
       <c r="J37" s="29"/>
       <c r="K37" s="27"/>
       <c r="L37" s="100"/>
@@ -11203,27 +11254,31 @@
     <row r="38" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7040</v>
+        <v>6759</v>
       </c>
       <c r="B38" s="51" t="s">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="C38" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="50">
-        <v>1001025027040</v>
+        <v>1001020836759</v>
       </c>
       <c r="E38" s="24"/>
       <c r="F38" s="125">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
+      <c r="H38" s="29">
+        <v>2.8</v>
+      </c>
+      <c r="I38" s="29">
+        <v>30</v>
+      </c>
       <c r="J38" s="29"/>
       <c r="K38" s="27"/>
       <c r="L38" s="100"/>
@@ -11286,27 +11341,27 @@
     <row r="39" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6759</v>
+        <v>6761</v>
       </c>
       <c r="B39" s="51" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D39" s="50">
-        <v>1001020836759</v>
+        <v>1001020836761</v>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="125">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G39" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G39:G40" si="7">E39</f>
         <v>0</v>
       </c>
       <c r="H39" s="29">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I39" s="29">
         <v>30</v>
@@ -11373,30 +11428,30 @@
     <row r="40" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6761</v>
+        <v>6829</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="C40" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D40" s="50">
-        <v>1001020836761</v>
+        <v>1001024976829</v>
       </c>
       <c r="E40" s="24"/>
       <c r="F40" s="125">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="G40" s="23">
-        <f t="shared" ref="G40:G41" si="7">E40</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H40" s="29">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="I40" s="29">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J40" s="29"/>
       <c r="K40" s="27"/>
@@ -11460,27 +11515,27 @@
     <row r="41" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6829</v>
+        <v>6616</v>
       </c>
       <c r="B41" s="51" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D41" s="50">
-        <v>1001024976829</v>
+        <v>1001024976616</v>
       </c>
       <c r="E41" s="24"/>
       <c r="F41" s="125">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="G41" s="23">
-        <f t="shared" si="7"/>
+        <f>E41*F41</f>
         <v>0</v>
       </c>
       <c r="H41" s="29">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="I41" s="29">
         <v>45</v>
@@ -11547,30 +11602,30 @@
     <row r="42" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6616</v>
+        <v>7075</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D42" s="50">
-        <v>1001024976616</v>
+        <v>1001022657075</v>
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="125">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G42" s="23">
-        <f>E42*F42</f>
+        <f>E42</f>
         <v>0</v>
       </c>
       <c r="H42" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I42" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J42" s="29"/>
       <c r="K42" s="27"/>
@@ -11634,27 +11689,27 @@
     <row r="43" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7075</v>
+        <v>7074</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D43" s="50">
-        <v>1001022657075</v>
+        <v>1001022657074</v>
       </c>
       <c r="E43" s="24"/>
       <c r="F43" s="125">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G43" s="23">
-        <f>E43</f>
+        <f t="shared" ref="G43:G46" si="8">E43*F43</f>
         <v>0</v>
       </c>
       <c r="H43" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I43" s="29">
         <v>50</v>
@@ -11721,27 +11776,27 @@
     <row r="44" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7074</v>
+        <v>7073</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="C44" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D44" s="50">
-        <v>1001022657074</v>
+        <v>1001022657073</v>
       </c>
       <c r="E44" s="24"/>
       <c r="F44" s="125">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" ref="G44:G47" si="8">E44*F44</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H44" s="29">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="I44" s="29">
         <v>50</v>
@@ -11808,30 +11863,30 @@
     <row r="45" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7073</v>
+        <v>6724</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C45" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="50">
-        <v>1001022657073</v>
+        <v>1001020836724</v>
       </c>
       <c r="E45" s="24"/>
       <c r="F45" s="125">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="G45" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H45" s="29">
-        <v>2.8</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I45" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J45" s="29"/>
       <c r="K45" s="27"/>
@@ -11895,27 +11950,27 @@
     <row r="46" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6724</v>
+        <v>5819</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C46" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="50">
-        <v>1001020836724</v>
+        <v>1001022725819</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="125">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G46" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H46" s="29">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="I46" s="29">
         <v>45</v>
@@ -11982,27 +12037,27 @@
     <row r="47" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>5819</v>
+        <v>6303</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47" s="50">
-        <v>1001022725819</v>
+        <v>1001022726303</v>
       </c>
       <c r="E47" s="24"/>
       <c r="F47" s="125">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G47" s="23">
-        <f t="shared" si="8"/>
+        <f>E47</f>
         <v>0</v>
       </c>
       <c r="H47" s="29">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="I47" s="29">
         <v>45</v>
@@ -12069,30 +12124,30 @@
     <row r="48" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6303</v>
+        <v>7255</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D48" s="50">
-        <v>1001022726303</v>
+        <v>1001025507255</v>
       </c>
       <c r="E48" s="24"/>
       <c r="F48" s="125">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G48" s="23">
-        <f>E48</f>
+        <f>E48*F48</f>
         <v>0</v>
       </c>
       <c r="H48" s="29">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="I48" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J48" s="29"/>
       <c r="K48" s="27"/>
@@ -12156,27 +12211,27 @@
     <row r="49" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7255</v>
+        <v>7271</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D49" s="50">
-        <v>1001025507255</v>
+        <v>1001025507271</v>
       </c>
       <c r="E49" s="24"/>
       <c r="F49" s="125">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G49" s="23">
-        <f>E49*F49</f>
+        <f>E49</f>
         <v>0</v>
       </c>
       <c r="H49" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I49" s="29">
         <v>50</v>
@@ -12243,30 +12298,30 @@
     <row r="50" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7271</v>
+        <v>6765</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D50" s="50">
-        <v>1001025507271</v>
+        <v>1001023696765</v>
       </c>
       <c r="E50" s="24"/>
       <c r="F50" s="125">
-        <v>1.5</v>
+        <v>0.36</v>
       </c>
       <c r="G50" s="23">
-        <f>E50</f>
+        <f>E50*F50</f>
         <v>0</v>
       </c>
       <c r="H50" s="29">
-        <v>6</v>
+        <v>2.16</v>
       </c>
       <c r="I50" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="27"/>
@@ -12330,27 +12385,27 @@
     <row r="51" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6765</v>
+        <v>6767</v>
       </c>
       <c r="B51" s="51" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D51" s="50">
-        <v>1001023696765</v>
+        <v>1001023696767</v>
       </c>
       <c r="E51" s="24"/>
       <c r="F51" s="125">
-        <v>0.36</v>
+        <v>1.04</v>
       </c>
       <c r="G51" s="23">
-        <f>E51*F51</f>
+        <f>E51</f>
         <v>0</v>
       </c>
       <c r="H51" s="29">
-        <v>2.16</v>
+        <v>4.16</v>
       </c>
       <c r="I51" s="29">
         <v>45</v>
@@ -12417,27 +12472,27 @@
     <row r="52" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6767</v>
+        <v>6475</v>
       </c>
       <c r="B52" s="51" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" s="50">
-        <v>1001023696767</v>
+        <v>1001025176475</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="125">
-        <v>1.04</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="23">
-        <f>E52</f>
+        <f>E52*F52</f>
         <v>0</v>
       </c>
       <c r="H52" s="29">
-        <v>4.16</v>
+        <v>2.4</v>
       </c>
       <c r="I52" s="29">
         <v>45</v>
@@ -12504,30 +12559,30 @@
     <row r="53" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6475</v>
+        <v>7083</v>
       </c>
       <c r="B53" s="51" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D53" s="50">
-        <v>1001025176475</v>
+        <v>1001022467083</v>
       </c>
       <c r="E53" s="24"/>
       <c r="F53" s="125">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G53" s="23">
-        <f>E53*F53</f>
+        <f>E53</f>
         <v>0</v>
       </c>
       <c r="H53" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I53" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="27"/>
@@ -12591,27 +12646,27 @@
     <row r="54" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7083</v>
+        <v>7080</v>
       </c>
       <c r="B54" s="51" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D54" s="50">
-        <v>1001022467083</v>
+        <v>1001022467080</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="125">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G54" s="23">
-        <f>E54</f>
+        <f t="shared" ref="G54:G56" si="9">E54*F54</f>
         <v>0</v>
       </c>
       <c r="H54" s="29">
-        <v>6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I54" s="29">
         <v>50</v>
@@ -12675,120 +12730,64 @@
       <c r="BN54" s="100"/>
       <c r="BO54" s="100"/>
     </row>
-    <row r="55" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7080</v>
+        <v>7276</v>
       </c>
       <c r="B55" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C55" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="50">
-        <v>1001022467080</v>
+        <v>1001022467276</v>
       </c>
       <c r="E55" s="24"/>
       <c r="F55" s="125">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="G55" s="23">
-        <f t="shared" ref="G55:G57" si="9">E55*F55</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H55" s="29">
-        <v>4.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="I55" s="29">
         <v>50</v>
       </c>
       <c r="J55" s="29"/>
-      <c r="K55" s="27"/>
       <c r="L55" s="100"/>
-      <c r="M55" s="100"/>
-      <c r="N55" s="100"/>
-      <c r="O55" s="100"/>
-      <c r="P55" s="100"/>
-      <c r="Q55" s="100"/>
-      <c r="R55" s="100"/>
-      <c r="S55" s="100"/>
-      <c r="T55" s="100"/>
-      <c r="U55" s="100"/>
-      <c r="V55" s="100"/>
-      <c r="W55" s="100"/>
-      <c r="X55" s="100"/>
-      <c r="Y55" s="100"/>
-      <c r="Z55" s="100"/>
-      <c r="AA55" s="100"/>
-      <c r="AB55" s="100"/>
-      <c r="AC55" s="100"/>
-      <c r="AD55" s="100"/>
-      <c r="AE55" s="100"/>
-      <c r="AF55" s="100"/>
-      <c r="AG55" s="100"/>
-      <c r="AH55" s="100"/>
-      <c r="AI55" s="100"/>
-      <c r="AJ55" s="100"/>
-      <c r="AK55" s="100"/>
-      <c r="AL55" s="100"/>
-      <c r="AM55" s="100"/>
-      <c r="AN55" s="100"/>
-      <c r="AO55" s="100"/>
-      <c r="AP55" s="100"/>
-      <c r="AQ55" s="100"/>
-      <c r="AR55" s="100"/>
-      <c r="AS55" s="100"/>
-      <c r="AT55" s="100"/>
-      <c r="AU55" s="100"/>
-      <c r="AV55" s="100"/>
-      <c r="AW55" s="100"/>
-      <c r="AX55" s="100"/>
-      <c r="AY55" s="100"/>
-      <c r="AZ55" s="100"/>
-      <c r="BA55" s="100"/>
-      <c r="BB55" s="100"/>
-      <c r="BC55" s="100"/>
-      <c r="BD55" s="100"/>
-      <c r="BE55" s="100"/>
-      <c r="BF55" s="100"/>
-      <c r="BG55" s="100"/>
-      <c r="BH55" s="100"/>
-      <c r="BI55" s="100"/>
-      <c r="BJ55" s="100"/>
-      <c r="BK55" s="100"/>
-      <c r="BL55" s="100"/>
-      <c r="BM55" s="100"/>
-      <c r="BN55" s="100"/>
-      <c r="BO55" s="100"/>
     </row>
     <row r="56" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7276</v>
+        <v>6762</v>
       </c>
       <c r="B56" s="51" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C56" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="50">
-        <v>1001022467276</v>
+        <v>1001020846762</v>
       </c>
       <c r="E56" s="24"/>
       <c r="F56" s="125">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="G56" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H56" s="29">
-        <v>2.1</v>
+        <v>3.28</v>
       </c>
       <c r="I56" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J56" s="29"/>
       <c r="L56" s="100"/>
@@ -12796,29 +12795,29 @@
     <row r="57" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6762</v>
+        <v>6764</v>
       </c>
       <c r="B57" s="51" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D57" s="50">
-        <v>1001020846762</v>
+        <v>1001020846764</v>
       </c>
       <c r="E57" s="24"/>
-      <c r="F57" s="125">
-        <v>0.41</v>
+      <c r="F57" s="23">
+        <v>1</v>
       </c>
       <c r="G57" s="23">
-        <f t="shared" si="9"/>
+        <f>E57</f>
         <v>0</v>
       </c>
-      <c r="H57" s="29">
-        <v>3.28</v>
-      </c>
-      <c r="I57" s="29">
+      <c r="H57" s="14">
+        <v>4</v>
+      </c>
+      <c r="I57" s="14">
         <v>45</v>
       </c>
       <c r="J57" s="29"/>
@@ -12827,30 +12826,30 @@
     <row r="58" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6764</v>
+        <v>7066</v>
       </c>
       <c r="B58" s="51" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D58" s="50">
-        <v>1001020846764</v>
+        <v>1001022377066</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="23">
-        <v>1</v>
+        <v>0.41</v>
       </c>
       <c r="G58" s="23">
-        <f>E58</f>
+        <f>E58*F58</f>
         <v>0</v>
       </c>
       <c r="H58" s="14">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I58" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J58" s="29"/>
       <c r="L58" s="100"/>
@@ -12858,27 +12857,27 @@
     <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7066</v>
+        <v>7070</v>
       </c>
       <c r="B59" s="51" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D59" s="50">
-        <v>1001022377066</v>
+        <v>1001022377070</v>
       </c>
       <c r="E59" s="24"/>
       <c r="F59" s="23">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G59" s="23">
-        <f>E59*F59</f>
+        <f>E59</f>
         <v>0</v>
       </c>
       <c r="H59" s="14">
-        <v>4.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="I59" s="14">
         <v>50</v>
@@ -12889,88 +12888,88 @@
     <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7070</v>
+        <v>7490</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>44</v>
+        <v>219</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D60" s="50">
-        <v>1001022377070</v>
+        <v>1001027417490</v>
       </c>
       <c r="E60" s="24"/>
       <c r="F60" s="23">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G60" s="23">
-        <f>E60</f>
+        <f>E60*F60</f>
         <v>0</v>
       </c>
-      <c r="H60" s="14">
-        <v>6</v>
-      </c>
-      <c r="I60" s="14">
-        <v>50</v>
-      </c>
-      <c r="J60" s="29"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="29" t="str">
+        <f>VLOOKUP(D60,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6713</v>
+      </c>
       <c r="L60" s="100"/>
     </row>
     <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7490</v>
+        <v>6661</v>
       </c>
       <c r="B61" s="51" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D61" s="50">
-        <v>1001027417490</v>
+        <v>1001022246661</v>
       </c>
       <c r="E61" s="24"/>
       <c r="F61" s="23">
-        <v>0.41</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="23">
-        <f>E61*F61</f>
+        <f t="shared" ref="G61:G62" si="10">E61</f>
         <v>0</v>
       </c>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="29" t="str">
-        <f>VLOOKUP(D61,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6713</v>
-      </c>
+      <c r="H61" s="14">
+        <v>6</v>
+      </c>
+      <c r="I61" s="14">
+        <v>45</v>
+      </c>
+      <c r="J61" s="29"/>
       <c r="L61" s="100"/>
     </row>
     <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6661</v>
+        <v>6254</v>
       </c>
       <c r="B62" s="51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C62" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="50">
-        <v>1001022246661</v>
+        <v>1001022556254</v>
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23">
         <v>1.5</v>
       </c>
       <c r="G62" s="23">
-        <f t="shared" ref="G62:G63" si="10">E62</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H62" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I62" s="14">
         <v>45</v>
@@ -12981,27 +12980,27 @@
     <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6254</v>
+        <v>6837</v>
       </c>
       <c r="B63" s="51" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D63" s="50">
-        <v>1001022556254</v>
+        <v>1001022556837</v>
       </c>
       <c r="E63" s="24"/>
       <c r="F63" s="23">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G63" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G63:G64" si="11">E63*F63</f>
         <v>0</v>
       </c>
       <c r="H63" s="14">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="I63" s="14">
         <v>45</v>
@@ -13009,30 +13008,30 @@
       <c r="J63" s="29"/>
       <c r="L63" s="100"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6837</v>
+        <v>7044</v>
       </c>
       <c r="B64" s="51" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="50">
-        <v>1001022556837</v>
+        <v>1001025167044</v>
       </c>
       <c r="E64" s="24"/>
       <c r="F64" s="23">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="G64" s="23">
-        <f t="shared" ref="G64:G65" si="11">E64*F64</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H64" s="14">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="I64" s="14">
         <v>45</v>
@@ -13040,80 +13039,80 @@
       <c r="J64" s="29"/>
       <c r="L64" s="100"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="134" t="str">
+    <row r="65" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="43"/>
+      <c r="L65" s="100"/>
+    </row>
+    <row r="66" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7044</v>
-      </c>
-      <c r="B65" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65" s="50">
-        <v>1001025167044</v>
-      </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="23">
-        <v>0.32</v>
-      </c>
-      <c r="G65" s="23">
-        <f t="shared" si="11"/>
+        <v>6550</v>
+      </c>
+      <c r="B66" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" s="127" t="s">
+        <v>22</v>
+      </c>
+      <c r="D66" s="50">
+        <v>1001032736550</v>
+      </c>
+      <c r="E66" s="24"/>
+      <c r="F66" s="125">
+        <v>1</v>
+      </c>
+      <c r="G66" s="23">
+        <f t="shared" ref="G66:G69" si="12">E66</f>
         <v>0</v>
       </c>
-      <c r="H65" s="14">
-        <v>2.56</v>
-      </c>
-      <c r="I65" s="14">
+      <c r="H66" s="29">
+        <v>3</v>
+      </c>
+      <c r="I66" s="29">
         <v>45</v>
       </c>
-      <c r="J65" s="29"/>
-      <c r="L65" s="100"/>
-    </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B66" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="43"/>
+      <c r="J66" s="29"/>
       <c r="L66" s="100"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6550</v>
+        <v>6608</v>
       </c>
       <c r="B67" s="126" t="s">
-        <v>151</v>
-      </c>
-      <c r="C67" s="127" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D67" s="50">
-        <v>1001032736550</v>
+        <v>1001033856608</v>
       </c>
       <c r="E67" s="24"/>
-      <c r="F67" s="125">
+      <c r="F67" s="23">
         <v>1</v>
       </c>
       <c r="G67" s="23">
-        <f t="shared" ref="G67:G70" si="12">E67</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H67" s="29">
+      <c r="H67" s="14">
         <v>3</v>
       </c>
-      <c r="I67" s="29">
+      <c r="I67" s="14">
         <v>45</v>
       </c>
       <c r="J67" s="29"/>
@@ -13122,16 +13121,16 @@
     <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6608</v>
+        <v>7001</v>
       </c>
       <c r="B68" s="126" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C68" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D68" s="50">
-        <v>1001033856608</v>
+        <v>1001035937001</v>
       </c>
       <c r="E68" s="24"/>
       <c r="F68" s="23">
@@ -13153,16 +13152,16 @@
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>7001</v>
+        <v>6527</v>
       </c>
       <c r="B69" s="126" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C69" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D69" s="50">
-        <v>1001035937001</v>
+        <v>1001031076527</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="23">
@@ -13184,27 +13183,27 @@
     <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6527</v>
+        <v>6609</v>
       </c>
       <c r="B70" s="126" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C70" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D70" s="50">
-        <v>1001031076527</v>
+        <v>1001033856609</v>
       </c>
       <c r="E70" s="24"/>
       <c r="F70" s="23">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G70" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G70:G71" si="13">E70*F70</f>
         <v>0</v>
       </c>
       <c r="H70" s="14">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="I70" s="14">
         <v>45</v>
@@ -13212,109 +13211,109 @@
       <c r="J70" s="29"/>
       <c r="L70" s="100"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6609</v>
+        <v>7059</v>
       </c>
       <c r="B71" s="126" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C71" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D71" s="50">
-        <v>1001033856609</v>
+        <v>1001035277059</v>
       </c>
       <c r="E71" s="24"/>
       <c r="F71" s="23">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G71" s="23">
-        <f t="shared" ref="G71:G72" si="13">E71*F71</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H71" s="14">
         <v>2.4</v>
       </c>
       <c r="I71" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J71" s="29"/>
       <c r="L71" s="100"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="134" t="str">
-        <f t="shared" si="1"/>
-        <v>7059</v>
-      </c>
-      <c r="B72" s="126" t="s">
-        <v>154</v>
-      </c>
-      <c r="C72" s="49" t="s">
+    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="43"/>
+      <c r="L72" s="100"/>
+    </row>
+    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="134" t="str">
+        <f t="shared" ref="A73:A97" si="14">RIGHT(D73,4)</f>
+        <v>7564</v>
+      </c>
+      <c r="B73" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="50">
+        <v>1001303637564</v>
+      </c>
+      <c r="E73" s="24"/>
+      <c r="F73" s="23">
+        <v>0.84</v>
+      </c>
+      <c r="G73" s="23">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I73" s="14">
+        <v>45</v>
+      </c>
+      <c r="J73" s="29"/>
+      <c r="L73" s="100"/>
+    </row>
+    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="134" t="str">
+        <f t="shared" si="14"/>
+        <v>7603</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="50">
-        <v>1001035277059</v>
-      </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G72" s="23">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="14">
-        <v>2.4</v>
-      </c>
-      <c r="I72" s="14">
-        <v>60</v>
-      </c>
-      <c r="J72" s="29"/>
-      <c r="L72" s="100"/>
-    </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B73" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C73" s="42"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
-      <c r="J73" s="43"/>
-      <c r="L73" s="100"/>
-    </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="134" t="str">
-        <f t="shared" ref="A74:A98" si="14">RIGHT(D74,4)</f>
-        <v>7564</v>
-      </c>
-      <c r="B74" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C74" s="49" t="s">
-        <v>22</v>
-      </c>
       <c r="D74" s="50">
-        <v>1001303637564</v>
+        <v>1001303637603</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="23">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="G74" s="23">
-        <f>E74</f>
+        <f t="shared" ref="G74:G86" si="15">E74*F74</f>
         <v>0</v>
       </c>
       <c r="H74" s="14">
-        <v>5.04</v>
+        <v>2.64</v>
       </c>
       <c r="I74" s="14">
         <v>45</v>
@@ -13325,30 +13324,30 @@
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7603</v>
+        <v>7149</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="C75" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="50">
-        <v>1001303637603</v>
+        <v>1001303637149</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="23">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" ref="G75:G87" si="15">E75*F75</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H75" s="14">
-        <v>2.64</v>
+        <v>5.04</v>
       </c>
       <c r="I75" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J75" s="29"/>
       <c r="L75" s="100"/>
@@ -13356,30 +13355,30 @@
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7149</v>
+        <v>7233</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>19</v>
+        <v>202</v>
       </c>
       <c r="C76" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="50">
-        <v>1001303637149</v>
+        <v>1001303637233</v>
       </c>
       <c r="E76" s="24"/>
-      <c r="F76" s="23">
-        <v>0.84</v>
+      <c r="F76" s="125">
+        <v>0.31</v>
       </c>
       <c r="G76" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H76" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I76" s="14">
-        <v>50</v>
+      <c r="H76" s="29">
+        <v>2.48</v>
+      </c>
+      <c r="I76" s="29">
+        <v>45</v>
       </c>
       <c r="J76" s="29"/>
       <c r="L76" s="100"/>
@@ -13387,30 +13386,30 @@
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7233</v>
+        <v>7232</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="C77" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="50">
-        <v>1001303637233</v>
+        <v>1001302277232</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="125">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G77" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H77" s="29">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I77" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J77" s="29"/>
       <c r="L77" s="100"/>
@@ -13418,16 +13417,16 @@
     <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7232</v>
+        <v>7241</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C78" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="50">
-        <v>1001302277232</v>
+        <v>1001303107241</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="125">
@@ -13441,7 +13440,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I78" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J78" s="29"/>
       <c r="L78" s="100"/>
@@ -13449,27 +13448,27 @@
     <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7241</v>
+        <v>7133</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D79" s="50">
-        <v>1001303107241</v>
+        <v>1001300367133</v>
       </c>
       <c r="E79" s="24"/>
       <c r="F79" s="125">
-        <v>0.28000000000000003</v>
+        <v>0.84</v>
       </c>
       <c r="G79" s="23">
-        <f t="shared" si="15"/>
+        <f>E79</f>
         <v>0</v>
       </c>
       <c r="H79" s="29">
-        <v>2.2400000000000002</v>
+        <v>5.04</v>
       </c>
       <c r="I79" s="29">
         <v>45</v>
@@ -13480,86 +13479,86 @@
     <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7133</v>
+        <v>6946</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="C80" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D80" s="50">
-        <v>1001300367133</v>
+        <v>1001300456946</v>
       </c>
       <c r="E80" s="24"/>
-      <c r="F80" s="125">
-        <v>0.84</v>
-      </c>
+      <c r="F80" s="125"/>
       <c r="G80" s="23">
         <f>E80</f>
         <v>0</v>
       </c>
-      <c r="H80" s="29">
-        <v>5.04</v>
-      </c>
-      <c r="I80" s="29">
-        <v>45</v>
-      </c>
+      <c r="H80" s="29"/>
+      <c r="I80" s="29"/>
       <c r="J80" s="29"/>
       <c r="L80" s="100"/>
     </row>
     <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6946</v>
+        <v>6807</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D81" s="50">
-        <v>1001300456946</v>
+        <v>1001300366807</v>
       </c>
       <c r="E81" s="24"/>
-      <c r="F81" s="125"/>
+      <c r="F81" s="125">
+        <v>0.33</v>
+      </c>
       <c r="G81" s="23">
-        <f>E81</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H81" s="29"/>
-      <c r="I81" s="29"/>
+      <c r="H81" s="29">
+        <v>2.64</v>
+      </c>
+      <c r="I81" s="29">
+        <v>45</v>
+      </c>
       <c r="J81" s="29"/>
       <c r="L81" s="100"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6807</v>
+        <v>7154</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C82" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D82" s="50">
-        <v>1001300366807</v>
+        <v>1001300387154</v>
       </c>
       <c r="E82" s="24"/>
-      <c r="F82" s="125">
-        <v>0.33</v>
+      <c r="F82" s="23">
+        <v>0.35</v>
       </c>
       <c r="G82" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H82" s="29">
-        <v>2.64</v>
-      </c>
-      <c r="I82" s="29">
-        <v>45</v>
+      <c r="H82" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I82" s="14">
+        <v>50</v>
       </c>
       <c r="J82" s="29"/>
       <c r="L82" s="100"/>
@@ -13567,27 +13566,27 @@
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7154</v>
+        <v>7157</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C83" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D83" s="50">
-        <v>1001300387154</v>
+        <v>1001300387157</v>
       </c>
       <c r="E83" s="24"/>
       <c r="F83" s="23">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="G83" s="23">
-        <f t="shared" si="15"/>
+        <f>E83</f>
         <v>0</v>
       </c>
       <c r="H83" s="14">
-        <v>2.8</v>
+        <v>5.04</v>
       </c>
       <c r="I83" s="14">
         <v>50</v>
@@ -13598,86 +13597,86 @@
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7157</v>
+        <v>7562</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="C84" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D84" s="50">
-        <v>1001300387157</v>
+        <v>1001307587562</v>
       </c>
       <c r="E84" s="24"/>
-      <c r="F84" s="23">
-        <v>0.63</v>
-      </c>
+      <c r="F84" s="23"/>
       <c r="G84" s="23">
         <f>E84</f>
         <v>0</v>
       </c>
-      <c r="H84" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I84" s="14">
-        <v>50</v>
-      </c>
-      <c r="J84" s="29"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="29" t="str">
+        <f>VLOOKUP(D84,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L84" s="100"/>
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7562</v>
+        <v>7236</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>213</v>
+        <v>68</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D85" s="50">
-        <v>1001307587562</v>
+        <v>1001304507236</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="23"/>
+      <c r="F85" s="23">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="G85" s="23">
-        <f>E85</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="29" t="str">
-        <f>VLOOKUP(D85,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H85" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I85" s="14">
+        <v>45</v>
+      </c>
+      <c r="J85" s="29"/>
       <c r="L85" s="100"/>
     </row>
-    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7236</v>
-      </c>
-      <c r="B86" s="51" t="s">
-        <v>68</v>
+        <v>6787</v>
+      </c>
+      <c r="B86" s="128" t="s">
+        <v>65</v>
       </c>
       <c r="C86" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="50">
-        <v>1001304507236</v>
+        <v>1001300456787</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="G86" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H86" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.64</v>
       </c>
       <c r="I86" s="14">
         <v>45</v>
@@ -13688,30 +13687,30 @@
     <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6787</v>
+        <v>7166</v>
       </c>
       <c r="B87" s="128" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D87" s="50">
-        <v>1001300456787</v>
+        <v>1001303987166</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="23">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="G87" s="23">
-        <f t="shared" si="15"/>
+        <f>E87</f>
         <v>0</v>
       </c>
       <c r="H87" s="14">
-        <v>2.64</v>
+        <v>5.6</v>
       </c>
       <c r="I87" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J87" s="29"/>
       <c r="L87" s="100"/>
@@ -13719,27 +13718,27 @@
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7166</v>
-      </c>
-      <c r="B88" s="128" t="s">
-        <v>71</v>
+        <v>7169</v>
+      </c>
+      <c r="B88" s="51" t="s">
+        <v>70</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" s="50">
-        <v>1001303987166</v>
+        <v>1001303987169</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="23">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="G88" s="23">
-        <f>E88</f>
+        <f>E88*F88</f>
         <v>0</v>
       </c>
       <c r="H88" s="14">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="I88" s="14">
         <v>50</v>
@@ -13750,16 +13749,16 @@
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7169</v>
+        <v>7156</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>70</v>
+        <v>206</v>
       </c>
       <c r="C89" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="50">
-        <v>1001303987169</v>
+        <v>1001304237156</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
@@ -13769,69 +13768,69 @@
         <f>E89*F89</f>
         <v>0</v>
       </c>
-      <c r="H89" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I89" s="14">
-        <v>50</v>
-      </c>
-      <c r="J89" s="29"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="29" t="str">
+        <f>VLOOKUP(D89,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L89" s="100"/>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7156</v>
+        <v>5544</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D90" s="50">
-        <v>1001304237156</v>
+        <v>1001051875544</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G90" s="23">
-        <f>E90*F90</f>
+        <f>E90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="29" t="str">
-        <f>VLOOKUP(D90,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H90" s="14">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="I90" s="14">
+        <v>45</v>
+      </c>
+      <c r="J90" s="29"/>
       <c r="L90" s="100"/>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>5544</v>
+        <v>6697</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C91" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D91" s="50">
-        <v>1001051875544</v>
+        <v>1001301876697</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G91" s="23">
-        <f>E91</f>
+        <f t="shared" ref="G91:G97" si="16">E91*F91</f>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I91" s="14">
         <v>45</v>
@@ -13842,27 +13841,27 @@
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6697</v>
+        <v>7238</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="C92" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="50">
-        <v>1001301876697</v>
+        <v>1001305197238</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92:G98" si="16">E92*F92</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H92" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I92" s="14">
         <v>45</v>
@@ -13873,16 +13872,16 @@
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7238</v>
+        <v>7516</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="C93" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="50">
-        <v>1001305197238</v>
+        <v>1001307107516</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
@@ -13892,35 +13891,34 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H93" s="14">
-        <v>2.48</v>
-      </c>
-      <c r="I93" s="14">
-        <v>45</v>
-      </c>
-      <c r="J93" s="29"/>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
+      <c r="J93" s="29" t="str">
+        <f>VLOOKUP(D93,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L93" s="100"/>
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7516</v>
+        <v>7710</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C94" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="50">
-        <v>1001307107516</v>
+        <v>1001307587710</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G94" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G94" si="17">E94*F94</f>
         <v>0</v>
       </c>
       <c r="H94" s="14"/>
@@ -13934,23 +13932,23 @@
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7710</v>
+        <v>7513</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C95" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="50">
-        <v>1001307587710</v>
+        <v>1001307077513</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.3</v>
+        <v>0.26</v>
       </c>
       <c r="G95" s="23">
-        <f t="shared" ref="G95" si="17">E95*F95</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H95" s="14"/>
@@ -13964,194 +13962,195 @@
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7177</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="C96" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="50">
-        <v>1001307077513</v>
+        <v>1001302347177</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="G96" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="14"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="29" t="str">
-        <f>VLOOKUP(D96,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H96" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I96" s="14">
+        <v>50</v>
+      </c>
+      <c r="J96" s="29"/>
       <c r="L96" s="100"/>
     </row>
-    <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7608</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="C97" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="50">
-        <v>1001302347177</v>
+        <v>1001304197608</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="G97" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="I97" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J97" s="29"/>
+      <c r="K97" s="27"/>
       <c r="L97" s="100"/>
-    </row>
-    <row r="98" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="134" t="str">
-        <f t="shared" si="14"/>
-        <v>7608</v>
-      </c>
-      <c r="B98" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="C98" s="49" t="s">
+      <c r="M97" s="100"/>
+      <c r="N97" s="100"/>
+      <c r="O97" s="100"/>
+      <c r="P97" s="100"/>
+      <c r="Q97" s="100"/>
+      <c r="R97" s="100"/>
+      <c r="S97" s="100"/>
+      <c r="T97" s="100"/>
+      <c r="U97" s="100"/>
+      <c r="V97" s="100"/>
+      <c r="W97" s="100"/>
+      <c r="X97" s="100"/>
+      <c r="Y97" s="100"/>
+      <c r="Z97" s="100"/>
+      <c r="AA97" s="100"/>
+      <c r="AB97" s="100"/>
+      <c r="AC97" s="100"/>
+      <c r="AD97" s="100"/>
+      <c r="AE97" s="100"/>
+      <c r="AF97" s="100"/>
+      <c r="AG97" s="100"/>
+      <c r="AH97" s="100"/>
+      <c r="AI97" s="100"/>
+      <c r="AJ97" s="100"/>
+      <c r="AK97" s="100"/>
+      <c r="AL97" s="100"/>
+      <c r="AM97" s="100"/>
+      <c r="AN97" s="100"/>
+      <c r="AO97" s="100"/>
+      <c r="AP97" s="100"/>
+      <c r="AQ97" s="100"/>
+      <c r="AR97" s="100"/>
+      <c r="AS97" s="100"/>
+      <c r="AT97" s="100"/>
+      <c r="AU97" s="100"/>
+      <c r="AV97" s="100"/>
+      <c r="AW97" s="100"/>
+      <c r="AX97" s="100"/>
+      <c r="AY97" s="100"/>
+      <c r="AZ97" s="100"/>
+      <c r="BA97" s="100"/>
+      <c r="BB97" s="100"/>
+      <c r="BC97" s="100"/>
+      <c r="BD97" s="100"/>
+      <c r="BE97" s="100"/>
+      <c r="BF97" s="100"/>
+      <c r="BG97" s="100"/>
+      <c r="BH97" s="100"/>
+      <c r="BI97" s="100"/>
+      <c r="BJ97" s="100"/>
+      <c r="BK97" s="100"/>
+      <c r="BL97" s="100"/>
+      <c r="BM97" s="100"/>
+      <c r="BN97" s="100"/>
+      <c r="BO97" s="100"/>
+    </row>
+    <row r="98" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C98" s="42"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="42"/>
+      <c r="J98" s="43"/>
+      <c r="L98" s="100"/>
+    </row>
+    <row r="99" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="134" t="str">
+        <f t="shared" ref="A99:A125" si="18">RIGHT(D99,4)</f>
+        <v>3986</v>
+      </c>
+      <c r="B99" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D98" s="50">
-        <v>1001304197608</v>
-      </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="23">
-        <v>0.1</v>
-      </c>
-      <c r="G98" s="23">
-        <f t="shared" si="16"/>
+      <c r="D99" s="50">
+        <v>1001061973986</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="125">
+        <v>0.25</v>
+      </c>
+      <c r="G99" s="23">
+        <f t="shared" ref="G99:G104" si="19">E99*F99</f>
         <v>0</v>
       </c>
-      <c r="H98" s="14">
-        <v>1</v>
-      </c>
-      <c r="I98" s="14">
-        <v>45</v>
-      </c>
-      <c r="J98" s="29"/>
-      <c r="K98" s="27"/>
-      <c r="L98" s="100"/>
-      <c r="M98" s="100"/>
-      <c r="N98" s="100"/>
-      <c r="O98" s="100"/>
-      <c r="P98" s="100"/>
-      <c r="Q98" s="100"/>
-      <c r="R98" s="100"/>
-      <c r="S98" s="100"/>
-      <c r="T98" s="100"/>
-      <c r="U98" s="100"/>
-      <c r="V98" s="100"/>
-      <c r="W98" s="100"/>
-      <c r="X98" s="100"/>
-      <c r="Y98" s="100"/>
-      <c r="Z98" s="100"/>
-      <c r="AA98" s="100"/>
-      <c r="AB98" s="100"/>
-      <c r="AC98" s="100"/>
-      <c r="AD98" s="100"/>
-      <c r="AE98" s="100"/>
-      <c r="AF98" s="100"/>
-      <c r="AG98" s="100"/>
-      <c r="AH98" s="100"/>
-      <c r="AI98" s="100"/>
-      <c r="AJ98" s="100"/>
-      <c r="AK98" s="100"/>
-      <c r="AL98" s="100"/>
-      <c r="AM98" s="100"/>
-      <c r="AN98" s="100"/>
-      <c r="AO98" s="100"/>
-      <c r="AP98" s="100"/>
-      <c r="AQ98" s="100"/>
-      <c r="AR98" s="100"/>
-      <c r="AS98" s="100"/>
-      <c r="AT98" s="100"/>
-      <c r="AU98" s="100"/>
-      <c r="AV98" s="100"/>
-      <c r="AW98" s="100"/>
-      <c r="AX98" s="100"/>
-      <c r="AY98" s="100"/>
-      <c r="AZ98" s="100"/>
-      <c r="BA98" s="100"/>
-      <c r="BB98" s="100"/>
-      <c r="BC98" s="100"/>
-      <c r="BD98" s="100"/>
-      <c r="BE98" s="100"/>
-      <c r="BF98" s="100"/>
-      <c r="BG98" s="100"/>
-      <c r="BH98" s="100"/>
-      <c r="BI98" s="100"/>
-      <c r="BJ98" s="100"/>
-      <c r="BK98" s="100"/>
-      <c r="BL98" s="100"/>
-      <c r="BM98" s="100"/>
-      <c r="BN98" s="100"/>
-      <c r="BO98" s="100"/>
-    </row>
-    <row r="99" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B99" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C99" s="42"/>
-      <c r="D99" s="42"/>
-      <c r="E99" s="42"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="42"/>
-      <c r="H99" s="42"/>
-      <c r="I99" s="42"/>
-      <c r="J99" s="43"/>
+      <c r="H99" s="129">
+        <v>2</v>
+      </c>
+      <c r="I99" s="130">
+        <v>120</v>
+      </c>
+      <c r="J99" s="29"/>
       <c r="L99" s="100"/>
     </row>
-    <row r="100" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="134" t="str">
-        <f t="shared" ref="A100:A126" si="18">RIGHT(D100,4)</f>
-        <v>3986</v>
+        <f t="shared" si="18"/>
+        <v>5931</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C100" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="50">
-        <v>1001061973986</v>
+        <v>1001060755931</v>
       </c>
       <c r="E100" s="24"/>
-      <c r="F100" s="125">
-        <v>0.25</v>
+      <c r="F100" s="23">
+        <v>0.22</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" ref="G100:G105" si="19">E100*F100</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H100" s="129">
-        <v>2</v>
-      </c>
-      <c r="I100" s="130">
+      <c r="H100" s="95">
+        <v>1.76</v>
+      </c>
+      <c r="I100" s="14">
         <v>120</v>
       </c>
       <c r="J100" s="29"/>
@@ -14160,86 +14159,86 @@
     <row r="101" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>5931</v>
+        <v>7700</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D101" s="50">
-        <v>1001060755931</v>
+        <v>1001067977700</v>
       </c>
       <c r="E101" s="24"/>
-      <c r="F101" s="23">
-        <v>0.22</v>
-      </c>
+      <c r="F101" s="23"/>
       <c r="G101" s="23">
-        <f t="shared" si="19"/>
+        <f>E101</f>
         <v>0</v>
       </c>
-      <c r="H101" s="95">
-        <v>1.76</v>
-      </c>
-      <c r="I101" s="14">
-        <v>120</v>
-      </c>
-      <c r="J101" s="29"/>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="29" t="str">
+        <f>VLOOKUP(D101,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 5708</v>
+      </c>
       <c r="L101" s="100"/>
     </row>
     <row r="102" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7700</v>
+        <v>3287</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="C102" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D102" s="50">
-        <v>1001067977700</v>
+        <v>1001060763287</v>
       </c>
       <c r="E102" s="24"/>
-      <c r="F102" s="23"/>
+      <c r="F102" s="23">
+        <v>0.48799999999999999</v>
+      </c>
       <c r="G102" s="23">
-        <f>E102</f>
+        <f t="shared" ref="G102" si="20">E102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="14"/>
-      <c r="I102" s="14"/>
-      <c r="J102" s="29" t="str">
-        <f>VLOOKUP(D102,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 5708</v>
-      </c>
+      <c r="H102" s="14">
+        <v>3.9</v>
+      </c>
+      <c r="I102" s="14">
+        <v>120</v>
+      </c>
+      <c r="J102" s="29"/>
       <c r="L102" s="100"/>
     </row>
     <row r="103" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>3287</v>
+        <v>4993</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D103" s="50">
-        <v>1001060763287</v>
+        <v>1001060764993</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" ref="G103" si="20">E103</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="I103" s="14">
         <v>120</v>
@@ -14250,16 +14249,16 @@
     <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>4993</v>
+        <v>5483</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="C104" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="50">
-        <v>1001060764993</v>
+        <v>1001062505483</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
@@ -14281,27 +14280,27 @@
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>5483</v>
+        <v>4117</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C105" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D105" s="50">
-        <v>1001062505483</v>
+        <v>1001062504117</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.25</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G105:G106" si="21">E105</f>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -14312,27 +14311,27 @@
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>4117</v>
+        <v>0614</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="C106" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D106" s="50">
-        <v>1001062504117</v>
+        <v>1001060720614</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" ref="G106:G107" si="21">E106</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>3.95</v>
+        <v>3.64</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -14343,27 +14342,27 @@
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>0614</v>
+        <v>6967</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="C107" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D107" s="50">
-        <v>1001060720614</v>
+        <v>1001063656967</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G107:G115" si="22">E107*F107</f>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <v>3.64</v>
+        <v>2</v>
       </c>
       <c r="I107" s="14">
         <v>120</v>
@@ -14374,23 +14373,23 @@
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6967</v>
+        <v>6937</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="C108" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D108" s="50">
-        <v>1001063656967</v>
+        <v>1001063106937</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
         <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" ref="G108:G116" si="22">E108*F108</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
@@ -14405,27 +14404,27 @@
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6937</v>
+        <v>7143</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C109" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="50">
-        <v>1001063106937</v>
+        <v>1001060717143</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G109" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -14436,30 +14435,30 @@
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7143</v>
+        <v>7456</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C110" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="50">
-        <v>1001060717143</v>
+        <v>1001063097456</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G110" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I110" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J110" s="29"/>
       <c r="L110" s="100"/>
@@ -14467,27 +14466,27 @@
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7456</v>
+        <v>7364</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C111" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="50">
-        <v>1001063097456</v>
+        <v>1001063217364</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G111" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I111" s="14">
         <v>90</v>
@@ -14498,16 +14497,16 @@
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7364</v>
+        <v>7383</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C112" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="50">
-        <v>1001063217364</v>
+        <v>1001065467383</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
@@ -14529,30 +14528,30 @@
     <row r="113" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7383</v>
+        <v>7317</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C113" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="50">
-        <v>1001065467383</v>
+        <v>1001066567317</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G113" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I113" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J113" s="29"/>
       <c r="L113" s="100"/>
@@ -14560,27 +14559,27 @@
     <row r="114" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7317</v>
+        <v>7318</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C114" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="50">
-        <v>1001066567317</v>
+        <v>1001060727318</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G114" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -14591,27 +14590,27 @@
     <row r="115" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7318</v>
+        <v>7316</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C115" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="50">
-        <v>1001060727318</v>
+        <v>1001060727316</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G115" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -14622,30 +14621,30 @@
     <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7316</v>
+        <v>6832</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="C116" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D116" s="50">
-        <v>1001060727316</v>
+        <v>1001065616832</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.54</v>
+        <v>0.215</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G116:G117" si="23">E116</f>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>3.78</v>
+        <v>2.15</v>
       </c>
       <c r="I116" s="14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="J116" s="29"/>
       <c r="L116" s="100"/>
@@ -14653,23 +14652,23 @@
     <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6832</v>
+        <v>7299</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C117" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D117" s="50">
-        <v>1001065616832</v>
+        <v>1001060677299</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
         <v>0.215</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" ref="G117:G118" si="23">E117</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
@@ -14684,30 +14683,30 @@
     <row r="118" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7299</v>
+        <v>7386</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="C118" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D118" s="50">
-        <v>1001060677299</v>
+        <v>1001067017386</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.215</v>
+        <v>0.15</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G118:G125" si="24">E118*F118</f>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="I118" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118" s="100"/>
@@ -14715,30 +14714,30 @@
     <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7386</v>
+        <v>7613</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="C119" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="50">
-        <v>1001067017386</v>
+        <v>1001061977613</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" ref="G119:G126" si="24">E119*F119</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="I119" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="100"/>
@@ -14746,27 +14745,27 @@
     <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7613</v>
+        <v>7382</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="C120" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="50">
-        <v>1001061977613</v>
+        <v>1001203117382</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G120" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I120" s="14">
         <v>60</v>
@@ -14777,27 +14776,27 @@
     <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7382</v>
+        <v>7616</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C121" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="50">
-        <v>1001203117382</v>
+        <v>1001062507616</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G121" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>0.96</v>
+        <v>1.4</v>
       </c>
       <c r="I121" s="14">
         <v>60</v>
@@ -14808,27 +14807,27 @@
     <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7616</v>
+        <v>6221</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="C122" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="50">
-        <v>1001062507616</v>
+        <v>1001205376221</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G122" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I122" s="14">
         <v>60</v>
@@ -14839,16 +14838,16 @@
     <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6221</v>
+        <v>6222</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C123" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="50">
-        <v>1001205376221</v>
+        <v>1001205386222</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
@@ -14867,30 +14866,30 @@
       <c r="J123" s="29"/>
       <c r="L123" s="100"/>
     </row>
-    <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6222</v>
+        <v>5679</v>
       </c>
       <c r="B124" s="51" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C124" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="50">
-        <v>1001205386222</v>
+        <v>1001190765679</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G124" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I124" s="14">
         <v>60</v>
@@ -14898,66 +14897,108 @@
       <c r="J124" s="29"/>
       <c r="L124" s="100"/>
     </row>
-    <row r="125" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>5679</v>
+        <v>7626</v>
       </c>
       <c r="B125" s="51" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="C125" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="50">
-        <v>1001190765679</v>
+        <v>1001066607626</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
       <c r="J125" s="29"/>
+      <c r="K125" s="27"/>
       <c r="L125" s="100"/>
-    </row>
-    <row r="126" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="134" t="str">
-        <f t="shared" si="18"/>
-        <v>7626</v>
-      </c>
-      <c r="B126" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C126" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D126" s="50">
-        <v>1001066607626</v>
-      </c>
-      <c r="E126" s="24"/>
-      <c r="F126" s="23">
-        <v>0.1</v>
-      </c>
-      <c r="G126" s="23">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="H126" s="14">
-        <v>1</v>
-      </c>
-      <c r="I126" s="14">
-        <v>60</v>
-      </c>
-      <c r="J126" s="29"/>
+      <c r="M125" s="100"/>
+      <c r="N125" s="100"/>
+      <c r="O125" s="100"/>
+      <c r="P125" s="100"/>
+      <c r="Q125" s="100"/>
+      <c r="R125" s="100"/>
+      <c r="S125" s="100"/>
+      <c r="T125" s="100"/>
+      <c r="U125" s="100"/>
+      <c r="V125" s="100"/>
+      <c r="W125" s="100"/>
+      <c r="X125" s="100"/>
+      <c r="Y125" s="100"/>
+      <c r="Z125" s="100"/>
+      <c r="AA125" s="100"/>
+      <c r="AB125" s="100"/>
+      <c r="AC125" s="100"/>
+      <c r="AD125" s="100"/>
+      <c r="AE125" s="100"/>
+      <c r="AF125" s="100"/>
+      <c r="AG125" s="100"/>
+      <c r="AH125" s="100"/>
+      <c r="AI125" s="100"/>
+      <c r="AJ125" s="100"/>
+      <c r="AK125" s="100"/>
+      <c r="AL125" s="100"/>
+      <c r="AM125" s="100"/>
+      <c r="AN125" s="100"/>
+      <c r="AO125" s="100"/>
+      <c r="AP125" s="100"/>
+      <c r="AQ125" s="100"/>
+      <c r="AR125" s="100"/>
+      <c r="AS125" s="100"/>
+      <c r="AT125" s="100"/>
+      <c r="AU125" s="100"/>
+      <c r="AV125" s="100"/>
+      <c r="AW125" s="100"/>
+      <c r="AX125" s="100"/>
+      <c r="AY125" s="100"/>
+      <c r="AZ125" s="100"/>
+      <c r="BA125" s="100"/>
+      <c r="BB125" s="100"/>
+      <c r="BC125" s="100"/>
+      <c r="BD125" s="100"/>
+      <c r="BE125" s="100"/>
+      <c r="BF125" s="100"/>
+      <c r="BG125" s="100"/>
+      <c r="BH125" s="100"/>
+      <c r="BI125" s="100"/>
+      <c r="BJ125" s="100"/>
+      <c r="BK125" s="100"/>
+      <c r="BL125" s="100"/>
+      <c r="BM125" s="100"/>
+      <c r="BN125" s="100"/>
+      <c r="BO125" s="100"/>
+    </row>
+    <row r="126" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C126" s="42"/>
+      <c r="D126" s="42"/>
+      <c r="E126" s="42"/>
+      <c r="F126" s="41"/>
+      <c r="G126" s="42"/>
+      <c r="H126" s="42"/>
+      <c r="I126" s="42"/>
+      <c r="J126" s="43"/>
       <c r="K126" s="27"/>
       <c r="L126" s="100"/>
       <c r="M126" s="100"/>
@@ -15016,21 +15057,35 @@
       <c r="BN126" s="100"/>
       <c r="BO126" s="100"/>
     </row>
-    <row r="127" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B127" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" s="42"/>
-      <c r="D127" s="42"/>
-      <c r="E127" s="42"/>
-      <c r="F127" s="41"/>
-      <c r="G127" s="42"/>
-      <c r="H127" s="42"/>
-      <c r="I127" s="42"/>
-      <c r="J127" s="43"/>
+    <row r="127" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="134" t="str">
+        <f t="shared" ref="A127:A138" si="25">RIGHT(D127,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B127" s="96" t="s">
+        <v>203</v>
+      </c>
+      <c r="C127" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D127" s="131">
+        <v>1001092674584</v>
+      </c>
+      <c r="E127" s="24"/>
+      <c r="F127" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="G127" s="23">
+        <f>E127</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I127" s="14">
+        <v>60</v>
+      </c>
+      <c r="J127" s="29"/>
       <c r="K127" s="27"/>
       <c r="L127" s="100"/>
       <c r="M127" s="100"/>
@@ -15089,35 +15144,34 @@
       <c r="BN127" s="100"/>
       <c r="BO127" s="100"/>
     </row>
-    <row r="128" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="134" t="str">
-        <f t="shared" ref="A128:A139" si="25">RIGHT(D128,4)</f>
-        <v>4584</v>
+        <f t="shared" si="25"/>
+        <v>7725</v>
       </c>
       <c r="B128" s="96" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C128" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D128" s="131">
-        <v>1001092674584</v>
+        <v>20</v>
+      </c>
+      <c r="D128" s="50">
+        <v>1001092437725</v>
       </c>
       <c r="E128" s="24"/>
-      <c r="F128" s="23">
-        <v>2.5</v>
+      <c r="F128" s="125">
+        <v>0.3</v>
       </c>
       <c r="G128" s="23">
-        <f>E128</f>
+        <f>E128*F128</f>
         <v>0</v>
       </c>
-      <c r="H128" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I128" s="14">
-        <v>60</v>
-      </c>
-      <c r="J128" s="29"/>
+      <c r="H128" s="29"/>
+      <c r="I128" s="29"/>
+      <c r="J128" s="29" t="str">
+        <f>VLOOKUP(D128,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6495</v>
+      </c>
       <c r="K128" s="27"/>
       <c r="L128" s="100"/>
       <c r="M128" s="100"/>
@@ -15176,34 +15230,35 @@
       <c r="BN128" s="100"/>
       <c r="BO128" s="100"/>
     </row>
-    <row r="129" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7725</v>
-      </c>
-      <c r="B129" s="96" t="s">
-        <v>218</v>
+        <v>5452</v>
+      </c>
+      <c r="B129" s="132" t="s">
+        <v>93</v>
       </c>
       <c r="C129" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D129" s="50">
-        <v>1001092437725</v>
+        <v>1001092485452</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="125">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="G129" s="23">
-        <f>E129*F129</f>
+        <f t="shared" ref="G129" si="26">E129</f>
         <v>0</v>
       </c>
-      <c r="H129" s="29"/>
-      <c r="I129" s="29"/>
-      <c r="J129" s="29" t="str">
-        <f>VLOOKUP(D129,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6495</v>
-      </c>
+      <c r="H129" s="29">
+        <v>4.05</v>
+      </c>
+      <c r="I129" s="29">
+        <v>60</v>
+      </c>
+      <c r="J129" s="29"/>
       <c r="K129" s="27"/>
       <c r="L129" s="100"/>
       <c r="M129" s="100"/>
@@ -15265,27 +15320,27 @@
     <row r="130" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>5452</v>
+        <v>3215</v>
       </c>
       <c r="B130" s="132" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="C130" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D130" s="50">
-        <v>1001092485452</v>
+        <v>1001094053215</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="125">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" ref="G130" si="26">E130</f>
+        <f>E130*F130</f>
         <v>0</v>
       </c>
       <c r="H130" s="29">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I130" s="29">
         <v>60</v>
@@ -15352,27 +15407,27 @@
     <row r="131" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>3215</v>
+        <v>6866</v>
       </c>
       <c r="B131" s="132" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="C131" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D131" s="50">
-        <v>1001094053215</v>
+        <v>1001095716866</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="125">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G131" s="23">
-        <f>E131*F131</f>
+        <f>E131</f>
         <v>0</v>
       </c>
       <c r="H131" s="29">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I131" s="29">
         <v>60</v>
@@ -15439,27 +15494,27 @@
     <row r="132" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6866</v>
-      </c>
-      <c r="B132" s="132" t="s">
-        <v>92</v>
+        <v>5495</v>
+      </c>
+      <c r="B132" s="51" t="s">
+        <v>94</v>
       </c>
       <c r="C132" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D132" s="50">
-        <v>1001095716866</v>
+        <v>20</v>
+      </c>
+      <c r="D132" s="133">
+        <v>1001093345495</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="125">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G132" s="23">
-        <f>E132</f>
+        <f t="shared" ref="G132:G133" si="27">E132*F132</f>
         <v>0</v>
       </c>
       <c r="H132" s="29">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I132" s="29">
         <v>60</v>
@@ -15526,30 +15581,30 @@
     <row r="133" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>5495</v>
+        <v>7377</v>
       </c>
       <c r="B133" s="51" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C133" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="133">
-        <v>1001093345495</v>
+        <v>1001095027377</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="125">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" ref="G133:G134" si="27">E133*F133</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H133" s="29">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I133" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J133" s="29"/>
       <c r="K133" s="27"/>
@@ -15610,33 +15665,33 @@
       <c r="BN133" s="100"/>
       <c r="BO133" s="100"/>
     </row>
-    <row r="134" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7377</v>
+        <v>6025</v>
       </c>
       <c r="B134" s="51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C134" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D134" s="133">
-        <v>1001095027377</v>
+        <v>1001094966025</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="125">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="27"/>
+        <f>E134</f>
         <v>0</v>
       </c>
       <c r="H134" s="29">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="I134" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J134" s="29"/>
       <c r="K134" s="27"/>
@@ -15697,161 +15752,104 @@
       <c r="BN134" s="100"/>
       <c r="BO134" s="100"/>
     </row>
-    <row r="135" spans="1:67" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6025</v>
+        <v>6929</v>
       </c>
       <c r="B135" s="51" t="s">
-        <v>118</v>
+        <v>210</v>
       </c>
       <c r="C135" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="133">
-        <v>1001094966025</v>
+        <v>1001085476929</v>
       </c>
       <c r="E135" s="24"/>
-      <c r="F135" s="125">
-        <v>3</v>
-      </c>
+      <c r="F135" s="125"/>
       <c r="G135" s="23">
         <f>E135</f>
         <v>0</v>
       </c>
-      <c r="H135" s="29">
-        <v>6</v>
-      </c>
-      <c r="I135" s="29">
-        <v>60</v>
-      </c>
-      <c r="J135" s="29"/>
-      <c r="K135" s="27"/>
+      <c r="H135" s="29"/>
+      <c r="I135" s="29"/>
+      <c r="J135" s="29" t="str">
+        <f>VLOOKUP(D135,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L135" s="100"/>
-      <c r="M135" s="100"/>
-      <c r="N135" s="100"/>
-      <c r="O135" s="100"/>
-      <c r="P135" s="100"/>
-      <c r="Q135" s="100"/>
-      <c r="R135" s="100"/>
-      <c r="S135" s="100"/>
-      <c r="T135" s="100"/>
-      <c r="U135" s="100"/>
-      <c r="V135" s="100"/>
-      <c r="W135" s="100"/>
-      <c r="X135" s="100"/>
-      <c r="Y135" s="100"/>
-      <c r="Z135" s="100"/>
-      <c r="AA135" s="100"/>
-      <c r="AB135" s="100"/>
-      <c r="AC135" s="100"/>
-      <c r="AD135" s="100"/>
-      <c r="AE135" s="100"/>
-      <c r="AF135" s="100"/>
-      <c r="AG135" s="100"/>
-      <c r="AH135" s="100"/>
-      <c r="AI135" s="100"/>
-      <c r="AJ135" s="100"/>
-      <c r="AK135" s="100"/>
-      <c r="AL135" s="100"/>
-      <c r="AM135" s="100"/>
-      <c r="AN135" s="100"/>
-      <c r="AO135" s="100"/>
-      <c r="AP135" s="100"/>
-      <c r="AQ135" s="100"/>
-      <c r="AR135" s="100"/>
-      <c r="AS135" s="100"/>
-      <c r="AT135" s="100"/>
-      <c r="AU135" s="100"/>
-      <c r="AV135" s="100"/>
-      <c r="AW135" s="100"/>
-      <c r="AX135" s="100"/>
-      <c r="AY135" s="100"/>
-      <c r="AZ135" s="100"/>
-      <c r="BA135" s="100"/>
-      <c r="BB135" s="100"/>
-      <c r="BC135" s="100"/>
-      <c r="BD135" s="100"/>
-      <c r="BE135" s="100"/>
-      <c r="BF135" s="100"/>
-      <c r="BG135" s="100"/>
-      <c r="BH135" s="100"/>
-      <c r="BI135" s="100"/>
-      <c r="BJ135" s="100"/>
-      <c r="BK135" s="100"/>
-      <c r="BL135" s="100"/>
-      <c r="BM135" s="100"/>
-      <c r="BN135" s="100"/>
-      <c r="BO135" s="100"/>
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6929</v>
+        <v>7485</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C136" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D136" s="133">
-        <v>1001085476929</v>
+        <v>1001107397485</v>
       </c>
       <c r="E136" s="24"/>
-      <c r="F136" s="125"/>
+      <c r="F136" s="125">
+        <v>0.15</v>
+      </c>
       <c r="G136" s="23">
-        <f>E136</f>
+        <f>F136*E136</f>
         <v>0</v>
       </c>
       <c r="H136" s="29"/>
       <c r="I136" s="29"/>
-      <c r="J136" s="29" t="str">
-        <f>VLOOKUP(D136,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="J136" s="29"/>
       <c r="L136" s="100"/>
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7485</v>
+        <v>7730</v>
       </c>
       <c r="B137" s="51" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C137" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="133">
-        <v>1001107397485</v>
+        <v>1001097747730</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="125">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G137" s="23">
-        <f>F137*E137</f>
+        <f>E137*F137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29"/>
       <c r="I137" s="29"/>
-      <c r="J137" s="29"/>
+      <c r="J137" s="29" t="str">
+        <f>VLOOKUP(D137,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 7647</v>
+      </c>
       <c r="L137" s="100"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7730</v>
+        <v>7731</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C138" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="133">
-        <v>1001097747730</v>
+        <v>1001097767731</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="125">
@@ -15861,85 +15859,86 @@
         <f>E138*F138</f>
         <v>0</v>
       </c>
-      <c r="H138" s="29"/>
-      <c r="I138" s="29"/>
+      <c r="H138" s="29">
+        <v>1</v>
+      </c>
+      <c r="I138" s="29">
+        <v>30</v>
+      </c>
       <c r="J138" s="29" t="str">
         <f>VLOOKUP(D138,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7647</v>
+        <v>Ротация кода 7651</v>
       </c>
       <c r="L138" s="100"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="134" t="str">
-        <f t="shared" si="25"/>
-        <v>7731</v>
-      </c>
-      <c r="B139" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="C139" s="49" t="s">
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B139" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="41"/>
+      <c r="G139" s="42"/>
+      <c r="H139" s="42"/>
+      <c r="I139" s="42"/>
+      <c r="J139" s="43"/>
+      <c r="L139" s="100"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="134" t="str">
+        <f t="shared" ref="A140:A152" si="28">RIGHT(D140,4)</f>
+        <v>7090</v>
+      </c>
+      <c r="B140" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C140" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="133">
-        <v>1001097767731</v>
-      </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="125">
-        <v>0.1</v>
-      </c>
-      <c r="G139" s="23">
-        <f>E139*F139</f>
+      <c r="D140" s="50">
+        <v>1001084217090</v>
+      </c>
+      <c r="E140" s="24"/>
+      <c r="F140" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="G140" s="23">
+        <f t="shared" ref="G140:G141" si="29">E140*F140</f>
         <v>0</v>
       </c>
-      <c r="H139" s="29">
-        <v>1</v>
-      </c>
-      <c r="I139" s="29">
-        <v>30</v>
-      </c>
-      <c r="J139" s="29" t="str">
-        <f>VLOOKUP(D139,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7651</v>
-      </c>
-      <c r="L139" s="100"/>
-    </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B140" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C140" s="42"/>
-      <c r="D140" s="42"/>
-      <c r="E140" s="42"/>
-      <c r="F140" s="41"/>
-      <c r="G140" s="42"/>
-      <c r="H140" s="42"/>
-      <c r="I140" s="42"/>
-      <c r="J140" s="43"/>
+      <c r="H140" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I140" s="14">
+        <v>50</v>
+      </c>
+      <c r="J140" s="29"/>
       <c r="L140" s="100"/>
     </row>
-    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="134" t="str">
-        <f t="shared" ref="A141:A153" si="28">RIGHT(D141,4)</f>
-        <v>7090</v>
+        <f t="shared" si="28"/>
+        <v>7187</v>
       </c>
       <c r="B141" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C141" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="50">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="23">
         <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" ref="G141:G142" si="29">E141*F141</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H141" s="14">
@@ -15954,30 +15953,30 @@
     <row r="142" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7187</v>
+        <v>6008</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="C142" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D142" s="50">
-        <v>1001085637187</v>
+        <v>1001084856008</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="23">
         <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" si="29"/>
+        <f>E142</f>
         <v>0</v>
       </c>
       <c r="H142" s="14">
         <v>1.8</v>
       </c>
       <c r="I142" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J142" s="29"/>
       <c r="L142" s="100"/>
@@ -15985,30 +15984,30 @@
     <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6008</v>
+        <v>6620</v>
       </c>
       <c r="B143" s="35" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
       <c r="C143" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="50">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="23">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G143" s="23">
         <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I143" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J143" s="29"/>
       <c r="L143" s="100"/>
@@ -16016,30 +16015,30 @@
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6620</v>
+        <v>7103</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D144" s="50">
-        <v>1001081596620</v>
+        <v>1001223297103</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="23">
-        <v>1.05</v>
+        <v>0.18</v>
       </c>
       <c r="G144" s="23">
-        <f>E144</f>
+        <f t="shared" ref="G144:G151" si="30">E144*F144</f>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I144" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J144" s="29"/>
       <c r="L144" s="100"/>
@@ -16047,27 +16046,27 @@
     <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7103</v>
+        <v>7092</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="C145" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D145" s="50">
-        <v>1001223297103</v>
+        <v>1001223297092</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="23">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" ref="G145:G152" si="30">E145*F145</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H145" s="14">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I145" s="14">
         <v>50</v>
@@ -16078,30 +16077,30 @@
     <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7092</v>
+        <v>6228</v>
       </c>
       <c r="B146" s="35" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C146" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D146" s="50">
-        <v>1001223297092</v>
+        <v>1001225416228</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G146" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H146" s="14">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I146" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J146" s="29"/>
       <c r="L146" s="100"/>
@@ -16109,174 +16108,172 @@
     <row r="147" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6228</v>
+        <v>6208</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C147" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="50">
-        <v>1001225416228</v>
+        <v>1001220226208</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G147" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H147" s="14">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I147" s="14">
         <v>45</v>
       </c>
       <c r="J147" s="29"/>
-      <c r="L147" s="100"/>
-    </row>
-    <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6208</v>
+        <v>6754</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="C148" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="50">
-        <v>1001220226208</v>
+        <v>1001225406754</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G148" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H148" s="14">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="I148" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J148" s="29"/>
     </row>
-    <row r="149" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6754</v>
+        <v>6279</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="C149" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="50">
-        <v>1001225406754</v>
+        <v>1001220286279</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="I149" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J149" s="29"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6279</v>
+        <v>7612</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="C150" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D150" s="50">
-        <v>1001220286279</v>
+        <v>1001453907612</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G150" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H150" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I150" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J150" s="29"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7612</v>
+        <v>7344</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C151" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="50">
-        <v>1001453907612</v>
+        <v>1001122287344</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>0.1</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G151" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H151" s="14">
-        <v>1</v>
-      </c>
-      <c r="I151" s="14">
-        <v>60</v>
-      </c>
-      <c r="J151" s="29"/>
-    </row>
-    <row r="152" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H151" s="14"/>
+      <c r="I151" s="14"/>
+      <c r="J151" s="29" t="str">
+        <f>VLOOKUP(D151,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7344</v>
+        <v>7345</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C152" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="50">
-        <v>1001122287344</v>
+        <v>1001123677345</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.33800000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="30"/>
+        <f>E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14"/>
@@ -16286,56 +16283,37 @@
         <v>Новинка</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="134" t="str">
-        <f t="shared" si="28"/>
-        <v>7345</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="C153" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D153" s="50">
-        <v>1001123677345</v>
-      </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="23">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="G153" s="23">
-        <f>E153*F153</f>
+    <row r="153" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="48"/>
+      <c r="B153" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C153" s="16"/>
+      <c r="D153" s="36"/>
+      <c r="E153" s="17">
+        <f>SUM(E10:E150)</f>
         <v>0</v>
       </c>
-      <c r="H153" s="14"/>
-      <c r="I153" s="14"/>
-      <c r="J153" s="29" t="str">
-        <f>VLOOKUP(D153,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="48"/>
-      <c r="B154" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C154" s="16"/>
-      <c r="D154" s="36"/>
-      <c r="E154" s="17">
-        <f>SUM(E10:E151)</f>
+      <c r="F153" s="17"/>
+      <c r="G153" s="17">
+        <f>SUM(G11:G152)</f>
         <v>0</v>
       </c>
-      <c r="F154" s="17"/>
-      <c r="G154" s="17">
-        <f>SUM(G11:G153)</f>
-        <v>0</v>
-      </c>
-      <c r="H154" s="17"/>
-      <c r="I154" s="17"/>
-      <c r="J154" s="17"/>
-    </row>
-    <row r="155" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H153" s="17"/>
+      <c r="I153" s="17"/>
+      <c r="J153" s="17"/>
+    </row>
+    <row r="154" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="37"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="40"/>
+      <c r="F154" s="19"/>
+      <c r="G154" s="19"/>
+      <c r="H154" s="20"/>
+      <c r="I154" s="20"/>
+      <c r="J154" s="21"/>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B155" s="37"/>
       <c r="C155" s="18"/>
       <c r="D155" s="40"/>
@@ -16347,12 +16325,13 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B156" s="37"/>
-      <c r="C156" s="18"/>
-      <c r="D156" s="40"/>
-      <c r="F156" s="19"/>
-      <c r="G156" s="19"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="20"/>
+      <c r="C156" s="53"/>
+      <c r="D156" s="54"/>
+      <c r="E156" s="55"/>
+      <c r="F156" s="56"/>
+      <c r="G156" s="56"/>
+      <c r="H156" s="57"/>
+      <c r="I156" s="57"/>
       <c r="J156" s="21"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -16369,23 +16348,22 @@
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B158" s="37"/>
       <c r="C158" s="53"/>
-      <c r="D158" s="54"/>
-      <c r="E158" s="55"/>
-      <c r="F158" s="56"/>
-      <c r="G158" s="56"/>
-      <c r="H158" s="57"/>
-      <c r="I158" s="57"/>
+      <c r="D158" s="58"/>
+      <c r="E158" s="59"/>
+      <c r="F158" s="58"/>
+      <c r="G158" s="60"/>
+      <c r="H158" s="61"/>
+      <c r="I158" s="62"/>
       <c r="J158" s="21"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B159" s="37"/>
-      <c r="C159" s="53"/>
-      <c r="D159" s="58"/>
-      <c r="E159" s="59"/>
-      <c r="F159" s="58"/>
-      <c r="G159" s="60"/>
-      <c r="H159" s="61"/>
-      <c r="I159" s="62"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="40"/>
+      <c r="F159" s="19"/>
+      <c r="G159" s="19"/>
+      <c r="H159" s="20"/>
+      <c r="I159" s="20"/>
       <c r="J159" s="21"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -31528,23 +31506,13 @@
       <c r="I1673" s="20"/>
       <c r="J1673" s="21"/>
     </row>
-    <row r="1674" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1674" s="37"/>
-      <c r="C1674" s="18"/>
-      <c r="D1674" s="40"/>
-      <c r="F1674" s="19"/>
-      <c r="G1674" s="19"/>
-      <c r="H1674" s="20"/>
-      <c r="I1674" s="20"/>
-      <c r="J1674" s="21"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:J154" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D159">
+  <conditionalFormatting sqref="D158">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -31556,7 +31524,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D159">
+  <conditionalFormatting sqref="D158">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DDA4D6-A2FA-4DB9-A057-9A7BBBE17824}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06173D8B-5CD9-41F1-8D19-C9C84B6D2F20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$153</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$585</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$585</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$154</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$586</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$586</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="224">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>ДОМАШНИЙ РЕЦЕПТ Коровино вар п/о_332к</t>
+  </si>
+  <si>
+    <t>САЛЯМИ ZHAZIRA ASLAM в/к в/у 0.82кг</t>
   </si>
 </sst>
 </file>
@@ -9212,7 +9215,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1673"/>
+  <dimension ref="A1:BO1674"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -13261,7 +13264,7 @@
     </row>
     <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A73" s="134" t="str">
-        <f t="shared" ref="A73:A97" si="14">RIGHT(D73,4)</f>
+        <f t="shared" ref="A73:A98" si="14">RIGHT(D73,4)</f>
         <v>7564</v>
       </c>
       <c r="B73" s="51" t="s">
@@ -13309,7 +13312,7 @@
         <v>0.33</v>
       </c>
       <c r="G74" s="23">
-        <f t="shared" ref="G74:G86" si="15">E74*F74</f>
+        <f t="shared" ref="G74:G87" si="15">E74*F74</f>
         <v>0</v>
       </c>
       <c r="H74" s="14">
@@ -13324,61 +13327,57 @@
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7149</v>
+        <v>7399</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="C75" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="50">
-        <v>1001303637149</v>
+        <v>1001057037399</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="23">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" si="15"/>
+        <f>E75*F75</f>
         <v>0</v>
       </c>
-      <c r="H75" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I75" s="14">
-        <v>50</v>
-      </c>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
       <c r="J75" s="29"/>
       <c r="L75" s="100"/>
     </row>
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7233</v>
+        <v>7149</v>
       </c>
       <c r="B76" s="51" t="s">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="C76" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="50">
-        <v>1001303637233</v>
+        <v>1001303637149</v>
       </c>
       <c r="E76" s="24"/>
-      <c r="F76" s="125">
-        <v>0.31</v>
+      <c r="F76" s="23">
+        <v>0.84</v>
       </c>
       <c r="G76" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H76" s="29">
-        <v>2.48</v>
-      </c>
-      <c r="I76" s="29">
-        <v>45</v>
+      <c r="H76" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I76" s="14">
+        <v>50</v>
       </c>
       <c r="J76" s="29"/>
       <c r="L76" s="100"/>
@@ -13386,30 +13385,30 @@
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7232</v>
+        <v>7233</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="C77" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="50">
-        <v>1001302277232</v>
+        <v>1001303637233</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="125">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G77" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H77" s="29">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I77" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J77" s="29"/>
       <c r="L77" s="100"/>
@@ -13417,16 +13416,16 @@
     <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7241</v>
+        <v>7232</v>
       </c>
       <c r="B78" s="51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C78" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="50">
-        <v>1001303107241</v>
+        <v>1001302277232</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="125">
@@ -13440,7 +13439,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I78" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J78" s="29"/>
       <c r="L78" s="100"/>
@@ -13448,27 +13447,27 @@
     <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7133</v>
+        <v>7241</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C79" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" s="50">
-        <v>1001300367133</v>
+        <v>1001303107241</v>
       </c>
       <c r="E79" s="24"/>
       <c r="F79" s="125">
-        <v>0.84</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G79" s="23">
-        <f>E79</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H79" s="29">
-        <v>5.04</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I79" s="29">
         <v>45</v>
@@ -13479,86 +13478,86 @@
     <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6946</v>
+        <v>7133</v>
       </c>
       <c r="B80" s="51" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="C80" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D80" s="50">
-        <v>1001300456946</v>
+        <v>1001300367133</v>
       </c>
       <c r="E80" s="24"/>
-      <c r="F80" s="125"/>
+      <c r="F80" s="125">
+        <v>0.84</v>
+      </c>
       <c r="G80" s="23">
         <f>E80</f>
         <v>0</v>
       </c>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
+      <c r="H80" s="29">
+        <v>5.04</v>
+      </c>
+      <c r="I80" s="29">
+        <v>45</v>
+      </c>
       <c r="J80" s="29"/>
       <c r="L80" s="100"/>
     </row>
     <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6807</v>
+        <v>6946</v>
       </c>
       <c r="B81" s="51" t="s">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="C81" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D81" s="50">
-        <v>1001300366807</v>
+        <v>1001300456946</v>
       </c>
       <c r="E81" s="24"/>
-      <c r="F81" s="125">
-        <v>0.33</v>
-      </c>
+      <c r="F81" s="125"/>
       <c r="G81" s="23">
-        <f t="shared" si="15"/>
+        <f>E81</f>
         <v>0</v>
       </c>
-      <c r="H81" s="29">
-        <v>2.64</v>
-      </c>
-      <c r="I81" s="29">
-        <v>45</v>
-      </c>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
       <c r="J81" s="29"/>
       <c r="L81" s="100"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7154</v>
+        <v>6807</v>
       </c>
       <c r="B82" s="51" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C82" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D82" s="50">
-        <v>1001300387154</v>
+        <v>1001300366807</v>
       </c>
       <c r="E82" s="24"/>
-      <c r="F82" s="23">
-        <v>0.35</v>
+      <c r="F82" s="125">
+        <v>0.33</v>
       </c>
       <c r="G82" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H82" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I82" s="14">
-        <v>50</v>
+      <c r="H82" s="29">
+        <v>2.64</v>
+      </c>
+      <c r="I82" s="29">
+        <v>45</v>
       </c>
       <c r="J82" s="29"/>
       <c r="L82" s="100"/>
@@ -13566,27 +13565,27 @@
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7157</v>
+        <v>7154</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C83" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D83" s="50">
-        <v>1001300387157</v>
+        <v>1001300387154</v>
       </c>
       <c r="E83" s="24"/>
       <c r="F83" s="23">
-        <v>0.63</v>
+        <v>0.35</v>
       </c>
       <c r="G83" s="23">
-        <f>E83</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H83" s="14">
-        <v>5.04</v>
+        <v>2.8</v>
       </c>
       <c r="I83" s="14">
         <v>50</v>
@@ -13597,86 +13596,86 @@
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7562</v>
+        <v>7157</v>
       </c>
       <c r="B84" s="51" t="s">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="C84" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D84" s="50">
-        <v>1001307587562</v>
+        <v>1001300387157</v>
       </c>
       <c r="E84" s="24"/>
-      <c r="F84" s="23"/>
+      <c r="F84" s="23">
+        <v>0.63</v>
+      </c>
       <c r="G84" s="23">
         <f>E84</f>
         <v>0</v>
       </c>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="29" t="str">
-        <f>VLOOKUP(D84,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H84" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I84" s="14">
+        <v>50</v>
+      </c>
+      <c r="J84" s="29"/>
       <c r="L84" s="100"/>
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7236</v>
+        <v>7562</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>68</v>
+        <v>213</v>
       </c>
       <c r="C85" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D85" s="50">
-        <v>1001304507236</v>
+        <v>1001307587562</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="23">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="F85" s="23"/>
       <c r="G85" s="23">
-        <f t="shared" si="15"/>
+        <f>E85</f>
         <v>0</v>
       </c>
-      <c r="H85" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I85" s="14">
-        <v>45</v>
-      </c>
-      <c r="J85" s="29"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="29" t="str">
+        <f>VLOOKUP(D85,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L85" s="100"/>
     </row>
-    <row r="86" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6787</v>
-      </c>
-      <c r="B86" s="128" t="s">
-        <v>65</v>
+        <v>7236</v>
+      </c>
+      <c r="B86" s="51" t="s">
+        <v>68</v>
       </c>
       <c r="C86" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="50">
-        <v>1001300456787</v>
+        <v>1001304507236</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H86" s="14">
-        <v>2.64</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I86" s="14">
         <v>45</v>
@@ -13687,30 +13686,30 @@
     <row r="87" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B87" s="128" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C87" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D87" s="50">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G87" s="23">
-        <f>E87</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H87" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I87" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J87" s="29"/>
       <c r="L87" s="100"/>
@@ -13718,27 +13717,27 @@
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7169</v>
-      </c>
-      <c r="B88" s="51" t="s">
-        <v>70</v>
+        <v>7166</v>
+      </c>
+      <c r="B88" s="128" t="s">
+        <v>71</v>
       </c>
       <c r="C88" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D88" s="50">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G88" s="23">
-        <f>E88*F88</f>
+        <f>E88</f>
         <v>0</v>
       </c>
       <c r="H88" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I88" s="14">
         <v>50</v>
@@ -13749,16 +13748,16 @@
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7156</v>
+        <v>7169</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>206</v>
+        <v>70</v>
       </c>
       <c r="C89" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="50">
-        <v>1001304237156</v>
+        <v>1001303987169</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
@@ -13768,69 +13767,69 @@
         <f>E89*F89</f>
         <v>0</v>
       </c>
-      <c r="H89" s="14"/>
-      <c r="I89" s="14"/>
-      <c r="J89" s="29" t="str">
-        <f>VLOOKUP(D89,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H89" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I89" s="14">
+        <v>50</v>
+      </c>
+      <c r="J89" s="29"/>
       <c r="L89" s="100"/>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>5544</v>
+        <v>7156</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="C90" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D90" s="50">
-        <v>1001051875544</v>
+        <v>1001304237156</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G90" s="23">
-        <f>E90</f>
+        <f>E90*F90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="14">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="I90" s="14">
-        <v>45</v>
-      </c>
-      <c r="J90" s="29"/>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
+      <c r="J90" s="29" t="str">
+        <f>VLOOKUP(D90,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L90" s="100"/>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C91" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D91" s="50">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G91" s="23">
-        <f t="shared" ref="G91:G97" si="16">E91*F91</f>
+        <f>E91</f>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I91" s="14">
         <v>45</v>
@@ -13841,27 +13840,27 @@
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7238</v>
+        <v>6697</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="C92" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="50">
-        <v>1001305197238</v>
+        <v>1001301876697</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G92:G98" si="16">E92*F92</f>
         <v>0</v>
       </c>
       <c r="H92" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I92" s="14">
         <v>45</v>
@@ -13872,16 +13871,16 @@
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7516</v>
+        <v>7238</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>212</v>
+        <v>123</v>
       </c>
       <c r="C93" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="50">
-        <v>1001307107516</v>
+        <v>1001305197238</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
@@ -13891,34 +13890,35 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="29" t="str">
-        <f>VLOOKUP(D93,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H93" s="14">
+        <v>2.48</v>
+      </c>
+      <c r="I93" s="14">
+        <v>45</v>
+      </c>
+      <c r="J93" s="29"/>
       <c r="L93" s="100"/>
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7710</v>
+        <v>7516</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C94" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="50">
-        <v>1001307587710</v>
+        <v>1001307107516</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="G94" s="23">
-        <f t="shared" ref="G94" si="17">E94*F94</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H94" s="14"/>
@@ -13932,23 +13932,23 @@
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7710</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C95" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="50">
-        <v>1001307077513</v>
+        <v>1001307587710</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G95" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G95" si="17">E95*F95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14"/>
@@ -13962,195 +13962,194 @@
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7513</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="C96" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="50">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G96" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I96" s="14">
-        <v>50</v>
-      </c>
-      <c r="J96" s="29"/>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
+      <c r="J96" s="29" t="str">
+        <f>VLOOKUP(D96,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L96" s="100"/>
     </row>
-    <row r="97" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="134" t="str">
         <f t="shared" si="14"/>
-        <v>7608</v>
+        <v>7177</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="C97" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="50">
-        <v>1001304197608</v>
+        <v>1001302347177</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I97" s="14">
+        <v>50</v>
+      </c>
+      <c r="J97" s="29"/>
+      <c r="L97" s="100"/>
+    </row>
+    <row r="98" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="134" t="str">
+        <f t="shared" si="14"/>
+        <v>7608</v>
+      </c>
+      <c r="B98" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="C98" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" s="50">
+        <v>1001304197608</v>
+      </c>
+      <c r="E98" s="24"/>
+      <c r="F98" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G98" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="14">
         <v>1</v>
       </c>
-      <c r="I97" s="14">
+      <c r="I98" s="14">
         <v>45</v>
       </c>
-      <c r="J97" s="29"/>
-      <c r="K97" s="27"/>
-      <c r="L97" s="100"/>
-      <c r="M97" s="100"/>
-      <c r="N97" s="100"/>
-      <c r="O97" s="100"/>
-      <c r="P97" s="100"/>
-      <c r="Q97" s="100"/>
-      <c r="R97" s="100"/>
-      <c r="S97" s="100"/>
-      <c r="T97" s="100"/>
-      <c r="U97" s="100"/>
-      <c r="V97" s="100"/>
-      <c r="W97" s="100"/>
-      <c r="X97" s="100"/>
-      <c r="Y97" s="100"/>
-      <c r="Z97" s="100"/>
-      <c r="AA97" s="100"/>
-      <c r="AB97" s="100"/>
-      <c r="AC97" s="100"/>
-      <c r="AD97" s="100"/>
-      <c r="AE97" s="100"/>
-      <c r="AF97" s="100"/>
-      <c r="AG97" s="100"/>
-      <c r="AH97" s="100"/>
-      <c r="AI97" s="100"/>
-      <c r="AJ97" s="100"/>
-      <c r="AK97" s="100"/>
-      <c r="AL97" s="100"/>
-      <c r="AM97" s="100"/>
-      <c r="AN97" s="100"/>
-      <c r="AO97" s="100"/>
-      <c r="AP97" s="100"/>
-      <c r="AQ97" s="100"/>
-      <c r="AR97" s="100"/>
-      <c r="AS97" s="100"/>
-      <c r="AT97" s="100"/>
-      <c r="AU97" s="100"/>
-      <c r="AV97" s="100"/>
-      <c r="AW97" s="100"/>
-      <c r="AX97" s="100"/>
-      <c r="AY97" s="100"/>
-      <c r="AZ97" s="100"/>
-      <c r="BA97" s="100"/>
-      <c r="BB97" s="100"/>
-      <c r="BC97" s="100"/>
-      <c r="BD97" s="100"/>
-      <c r="BE97" s="100"/>
-      <c r="BF97" s="100"/>
-      <c r="BG97" s="100"/>
-      <c r="BH97" s="100"/>
-      <c r="BI97" s="100"/>
-      <c r="BJ97" s="100"/>
-      <c r="BK97" s="100"/>
-      <c r="BL97" s="100"/>
-      <c r="BM97" s="100"/>
-      <c r="BN97" s="100"/>
-      <c r="BO97" s="100"/>
-    </row>
-    <row r="98" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="47" t="s">
+      <c r="J98" s="29"/>
+      <c r="K98" s="27"/>
+      <c r="L98" s="100"/>
+      <c r="M98" s="100"/>
+      <c r="N98" s="100"/>
+      <c r="O98" s="100"/>
+      <c r="P98" s="100"/>
+      <c r="Q98" s="100"/>
+      <c r="R98" s="100"/>
+      <c r="S98" s="100"/>
+      <c r="T98" s="100"/>
+      <c r="U98" s="100"/>
+      <c r="V98" s="100"/>
+      <c r="W98" s="100"/>
+      <c r="X98" s="100"/>
+      <c r="Y98" s="100"/>
+      <c r="Z98" s="100"/>
+      <c r="AA98" s="100"/>
+      <c r="AB98" s="100"/>
+      <c r="AC98" s="100"/>
+      <c r="AD98" s="100"/>
+      <c r="AE98" s="100"/>
+      <c r="AF98" s="100"/>
+      <c r="AG98" s="100"/>
+      <c r="AH98" s="100"/>
+      <c r="AI98" s="100"/>
+      <c r="AJ98" s="100"/>
+      <c r="AK98" s="100"/>
+      <c r="AL98" s="100"/>
+      <c r="AM98" s="100"/>
+      <c r="AN98" s="100"/>
+      <c r="AO98" s="100"/>
+      <c r="AP98" s="100"/>
+      <c r="AQ98" s="100"/>
+      <c r="AR98" s="100"/>
+      <c r="AS98" s="100"/>
+      <c r="AT98" s="100"/>
+      <c r="AU98" s="100"/>
+      <c r="AV98" s="100"/>
+      <c r="AW98" s="100"/>
+      <c r="AX98" s="100"/>
+      <c r="AY98" s="100"/>
+      <c r="AZ98" s="100"/>
+      <c r="BA98" s="100"/>
+      <c r="BB98" s="100"/>
+      <c r="BC98" s="100"/>
+      <c r="BD98" s="100"/>
+      <c r="BE98" s="100"/>
+      <c r="BF98" s="100"/>
+      <c r="BG98" s="100"/>
+      <c r="BH98" s="100"/>
+      <c r="BI98" s="100"/>
+      <c r="BJ98" s="100"/>
+      <c r="BK98" s="100"/>
+      <c r="BL98" s="100"/>
+      <c r="BM98" s="100"/>
+      <c r="BN98" s="100"/>
+      <c r="BO98" s="100"/>
+    </row>
+    <row r="99" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B98" s="42" t="s">
+      <c r="B99" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C98" s="42"/>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="42"/>
-      <c r="H98" s="42"/>
-      <c r="I98" s="42"/>
-      <c r="J98" s="43"/>
-      <c r="L98" s="100"/>
-    </row>
-    <row r="99" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="134" t="str">
-        <f t="shared" ref="A99:A125" si="18">RIGHT(D99,4)</f>
+      <c r="C99" s="42"/>
+      <c r="D99" s="42"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="42"/>
+      <c r="I99" s="42"/>
+      <c r="J99" s="43"/>
+      <c r="L99" s="100"/>
+    </row>
+    <row r="100" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="134" t="str">
+        <f t="shared" ref="A100:A126" si="18">RIGHT(D100,4)</f>
         <v>3986</v>
       </c>
-      <c r="B99" s="51" t="s">
+      <c r="B100" s="51" t="s">
         <v>79</v>
-      </c>
-      <c r="C99" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D99" s="50">
-        <v>1001061973986</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="125">
-        <v>0.25</v>
-      </c>
-      <c r="G99" s="23">
-        <f t="shared" ref="G99:G104" si="19">E99*F99</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="129">
-        <v>2</v>
-      </c>
-      <c r="I99" s="130">
-        <v>120</v>
-      </c>
-      <c r="J99" s="29"/>
-      <c r="L99" s="100"/>
-    </row>
-    <row r="100" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="134" t="str">
-        <f t="shared" si="18"/>
-        <v>5931</v>
-      </c>
-      <c r="B100" s="51" t="s">
-        <v>77</v>
       </c>
       <c r="C100" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="50">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E100" s="24"/>
-      <c r="F100" s="23">
-        <v>0.22</v>
+      <c r="F100" s="125">
+        <v>0.25</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G100:G105" si="19">E100*F100</f>
         <v>0</v>
       </c>
-      <c r="H100" s="95">
-        <v>1.76</v>
-      </c>
-      <c r="I100" s="14">
+      <c r="H100" s="129">
+        <v>2</v>
+      </c>
+      <c r="I100" s="130">
         <v>120</v>
       </c>
       <c r="J100" s="29"/>
@@ -14159,86 +14158,86 @@
     <row r="101" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7700</v>
+        <v>5931</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="C101" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D101" s="50">
-        <v>1001067977700</v>
+        <v>1001060755931</v>
       </c>
       <c r="E101" s="24"/>
-      <c r="F101" s="23"/>
+      <c r="F101" s="23">
+        <v>0.22</v>
+      </c>
       <c r="G101" s="23">
-        <f>E101</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H101" s="14"/>
-      <c r="I101" s="14"/>
-      <c r="J101" s="29" t="str">
-        <f>VLOOKUP(D101,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 5708</v>
-      </c>
+      <c r="H101" s="95">
+        <v>1.76</v>
+      </c>
+      <c r="I101" s="14">
+        <v>120</v>
+      </c>
+      <c r="J101" s="29"/>
       <c r="L101" s="100"/>
     </row>
     <row r="102" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>3287</v>
+        <v>7700</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>90</v>
+        <v>217</v>
       </c>
       <c r="C102" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D102" s="50">
-        <v>1001060763287</v>
+        <v>1001067977700</v>
       </c>
       <c r="E102" s="24"/>
-      <c r="F102" s="23">
-        <v>0.48799999999999999</v>
-      </c>
+      <c r="F102" s="23"/>
       <c r="G102" s="23">
-        <f t="shared" ref="G102" si="20">E102</f>
+        <f>E102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="14">
-        <v>3.9</v>
-      </c>
-      <c r="I102" s="14">
-        <v>120</v>
-      </c>
-      <c r="J102" s="29"/>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="29" t="str">
+        <f>VLOOKUP(D102,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 5708</v>
+      </c>
       <c r="L102" s="100"/>
     </row>
     <row r="103" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>4993</v>
+        <v>3287</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="C103" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D103" s="50">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G103" si="20">E103</f>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I103" s="14">
         <v>120</v>
@@ -14249,16 +14248,16 @@
     <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>5483</v>
+        <v>4993</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C104" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="50">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
@@ -14280,27 +14279,27 @@
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>4117</v>
+        <v>5483</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C105" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D105" s="50">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" ref="G105:G106" si="21">E105</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -14311,27 +14310,27 @@
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>0614</v>
+        <v>4117</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C106" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D106" s="50">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G106:G107" si="21">E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -14342,27 +14341,27 @@
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6967</v>
+        <v>0614</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C107" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D107" s="50">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" ref="G107:G115" si="22">E107*F107</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I107" s="14">
         <v>120</v>
@@ -14373,23 +14372,23 @@
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6937</v>
+        <v>6967</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C108" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D108" s="50">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
         <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G108:G116" si="22">E108*F108</f>
         <v>0</v>
       </c>
       <c r="H108" s="14">
@@ -14404,27 +14403,27 @@
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7143</v>
+        <v>6937</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C109" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="50">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G109" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -14435,30 +14434,30 @@
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7456</v>
+        <v>7143</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C110" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="50">
-        <v>1001063097456</v>
+        <v>1001060717143</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G110" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I110" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J110" s="29"/>
       <c r="L110" s="100"/>
@@ -14466,27 +14465,27 @@
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7364</v>
+        <v>7456</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C111" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="50">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G111" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I111" s="14">
         <v>90</v>
@@ -14497,16 +14496,16 @@
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7383</v>
+        <v>7364</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C112" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="50">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
@@ -14528,30 +14527,30 @@
     <row r="113" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7317</v>
+        <v>7383</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C113" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="50">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G113" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I113" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J113" s="29"/>
       <c r="L113" s="100"/>
@@ -14559,27 +14558,27 @@
     <row r="114" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7318</v>
+        <v>7317</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C114" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="50">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G114" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -14590,27 +14589,27 @@
     <row r="115" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7316</v>
+        <v>7318</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C115" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="50">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G115" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -14621,30 +14620,30 @@
     <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6832</v>
+        <v>7316</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="C116" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D116" s="50">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" ref="G116:G117" si="23">E116</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I116" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J116" s="29"/>
       <c r="L116" s="100"/>
@@ -14652,23 +14651,23 @@
     <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7299</v>
+        <v>6832</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C117" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D117" s="50">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
         <v>0.215</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G117:G118" si="23">E117</f>
         <v>0</v>
       </c>
       <c r="H117" s="14">
@@ -14683,30 +14682,30 @@
     <row r="118" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7386</v>
+        <v>7299</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C118" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D118" s="50">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" ref="G118:G125" si="24">E118*F118</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I118" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118" s="100"/>
@@ -14714,30 +14713,30 @@
     <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7613</v>
+        <v>7386</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="C119" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="50">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G119:G126" si="24">E119*F119</f>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I119" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="100"/>
@@ -14745,27 +14744,27 @@
     <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7382</v>
+        <v>7613</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="C120" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="50">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G120" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I120" s="14">
         <v>60</v>
@@ -14776,27 +14775,27 @@
     <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7616</v>
+        <v>7382</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="C121" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="50">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G121" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I121" s="14">
         <v>60</v>
@@ -14807,27 +14806,27 @@
     <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6221</v>
+        <v>7616</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="C122" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="50">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G122" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I122" s="14">
         <v>60</v>
@@ -14838,16 +14837,16 @@
     <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>6222</v>
+        <v>6221</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="C123" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="50">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
@@ -14866,30 +14865,30 @@
       <c r="J123" s="29"/>
       <c r="L123" s="100"/>
     </row>
-    <row r="124" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>5679</v>
+        <v>6222</v>
       </c>
       <c r="B124" s="51" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C124" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="50">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G124" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I124" s="14">
         <v>60</v>
@@ -14897,108 +14896,66 @@
       <c r="J124" s="29"/>
       <c r="L124" s="100"/>
     </row>
-    <row r="125" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="134" t="str">
         <f t="shared" si="18"/>
-        <v>7626</v>
+        <v>5679</v>
       </c>
       <c r="B125" s="51" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="C125" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="50">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
       <c r="J125" s="29"/>
-      <c r="K125" s="27"/>
       <c r="L125" s="100"/>
-      <c r="M125" s="100"/>
-      <c r="N125" s="100"/>
-      <c r="O125" s="100"/>
-      <c r="P125" s="100"/>
-      <c r="Q125" s="100"/>
-      <c r="R125" s="100"/>
-      <c r="S125" s="100"/>
-      <c r="T125" s="100"/>
-      <c r="U125" s="100"/>
-      <c r="V125" s="100"/>
-      <c r="W125" s="100"/>
-      <c r="X125" s="100"/>
-      <c r="Y125" s="100"/>
-      <c r="Z125" s="100"/>
-      <c r="AA125" s="100"/>
-      <c r="AB125" s="100"/>
-      <c r="AC125" s="100"/>
-      <c r="AD125" s="100"/>
-      <c r="AE125" s="100"/>
-      <c r="AF125" s="100"/>
-      <c r="AG125" s="100"/>
-      <c r="AH125" s="100"/>
-      <c r="AI125" s="100"/>
-      <c r="AJ125" s="100"/>
-      <c r="AK125" s="100"/>
-      <c r="AL125" s="100"/>
-      <c r="AM125" s="100"/>
-      <c r="AN125" s="100"/>
-      <c r="AO125" s="100"/>
-      <c r="AP125" s="100"/>
-      <c r="AQ125" s="100"/>
-      <c r="AR125" s="100"/>
-      <c r="AS125" s="100"/>
-      <c r="AT125" s="100"/>
-      <c r="AU125" s="100"/>
-      <c r="AV125" s="100"/>
-      <c r="AW125" s="100"/>
-      <c r="AX125" s="100"/>
-      <c r="AY125" s="100"/>
-      <c r="AZ125" s="100"/>
-      <c r="BA125" s="100"/>
-      <c r="BB125" s="100"/>
-      <c r="BC125" s="100"/>
-      <c r="BD125" s="100"/>
-      <c r="BE125" s="100"/>
-      <c r="BF125" s="100"/>
-      <c r="BG125" s="100"/>
-      <c r="BH125" s="100"/>
-      <c r="BI125" s="100"/>
-      <c r="BJ125" s="100"/>
-      <c r="BK125" s="100"/>
-      <c r="BL125" s="100"/>
-      <c r="BM125" s="100"/>
-      <c r="BN125" s="100"/>
-      <c r="BO125" s="100"/>
-    </row>
-    <row r="126" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B126" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C126" s="42"/>
-      <c r="D126" s="42"/>
-      <c r="E126" s="42"/>
-      <c r="F126" s="41"/>
-      <c r="G126" s="42"/>
-      <c r="H126" s="42"/>
-      <c r="I126" s="42"/>
-      <c r="J126" s="43"/>
+    </row>
+    <row r="126" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="134" t="str">
+        <f t="shared" si="18"/>
+        <v>7626</v>
+      </c>
+      <c r="B126" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="C126" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D126" s="50">
+        <v>1001066607626</v>
+      </c>
+      <c r="E126" s="24"/>
+      <c r="F126" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G126" s="23">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H126" s="14">
+        <v>1</v>
+      </c>
+      <c r="I126" s="14">
+        <v>60</v>
+      </c>
+      <c r="J126" s="29"/>
       <c r="K126" s="27"/>
       <c r="L126" s="100"/>
       <c r="M126" s="100"/>
@@ -15057,35 +15014,21 @@
       <c r="BN126" s="100"/>
       <c r="BO126" s="100"/>
     </row>
-    <row r="127" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="134" t="str">
-        <f t="shared" ref="A127:A138" si="25">RIGHT(D127,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B127" s="96" t="s">
-        <v>203</v>
-      </c>
-      <c r="C127" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D127" s="131">
-        <v>1001092674584</v>
-      </c>
-      <c r="E127" s="24"/>
-      <c r="F127" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="G127" s="23">
-        <f>E127</f>
-        <v>0</v>
-      </c>
-      <c r="H127" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I127" s="14">
-        <v>60</v>
-      </c>
-      <c r="J127" s="29"/>
+    <row r="127" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B127" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C127" s="42"/>
+      <c r="D127" s="42"/>
+      <c r="E127" s="42"/>
+      <c r="F127" s="41"/>
+      <c r="G127" s="42"/>
+      <c r="H127" s="42"/>
+      <c r="I127" s="42"/>
+      <c r="J127" s="43"/>
       <c r="K127" s="27"/>
       <c r="L127" s="100"/>
       <c r="M127" s="100"/>
@@ -15144,34 +15087,35 @@
       <c r="BN127" s="100"/>
       <c r="BO127" s="100"/>
     </row>
-    <row r="128" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A128" s="134" t="str">
-        <f t="shared" si="25"/>
-        <v>7725</v>
+        <f t="shared" ref="A128:A139" si="25">RIGHT(D128,4)</f>
+        <v>4584</v>
       </c>
       <c r="B128" s="96" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C128" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D128" s="50">
-        <v>1001092437725</v>
+        <v>22</v>
+      </c>
+      <c r="D128" s="131">
+        <v>1001092674584</v>
       </c>
       <c r="E128" s="24"/>
-      <c r="F128" s="125">
-        <v>0.3</v>
+      <c r="F128" s="23">
+        <v>2.5</v>
       </c>
       <c r="G128" s="23">
-        <f>E128*F128</f>
+        <f>E128</f>
         <v>0</v>
       </c>
-      <c r="H128" s="29"/>
-      <c r="I128" s="29"/>
-      <c r="J128" s="29" t="str">
-        <f>VLOOKUP(D128,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 6495</v>
-      </c>
+      <c r="H128" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I128" s="14">
+        <v>60</v>
+      </c>
+      <c r="J128" s="29"/>
       <c r="K128" s="27"/>
       <c r="L128" s="100"/>
       <c r="M128" s="100"/>
@@ -15230,35 +15174,34 @@
       <c r="BN128" s="100"/>
       <c r="BO128" s="100"/>
     </row>
-    <row r="129" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:67" s="52" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>5452</v>
-      </c>
-      <c r="B129" s="132" t="s">
-        <v>93</v>
+        <v>7725</v>
+      </c>
+      <c r="B129" s="96" t="s">
+        <v>218</v>
       </c>
       <c r="C129" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D129" s="50">
-        <v>1001092485452</v>
+        <v>1001092437725</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="125">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" ref="G129" si="26">E129</f>
+        <f>E129*F129</f>
         <v>0</v>
       </c>
-      <c r="H129" s="29">
-        <v>4.05</v>
-      </c>
-      <c r="I129" s="29">
-        <v>60</v>
-      </c>
-      <c r="J129" s="29"/>
+      <c r="H129" s="29"/>
+      <c r="I129" s="29"/>
+      <c r="J129" s="29" t="str">
+        <f>VLOOKUP(D129,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 6495</v>
+      </c>
       <c r="K129" s="27"/>
       <c r="L129" s="100"/>
       <c r="M129" s="100"/>
@@ -15320,27 +15263,27 @@
     <row r="130" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>3215</v>
+        <v>5452</v>
       </c>
       <c r="B130" s="132" t="s">
-        <v>198</v>
+        <v>93</v>
       </c>
       <c r="C130" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D130" s="50">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="125">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G130" s="23">
-        <f>E130*F130</f>
+        <f t="shared" ref="G130" si="26">E130</f>
         <v>0</v>
       </c>
       <c r="H130" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I130" s="29">
         <v>60</v>
@@ -15407,27 +15350,27 @@
     <row r="131" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6866</v>
+        <v>3215</v>
       </c>
       <c r="B131" s="132" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="C131" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D131" s="50">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="125">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G131" s="23">
-        <f>E131</f>
+        <f>E131*F131</f>
         <v>0</v>
       </c>
       <c r="H131" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I131" s="29">
         <v>60</v>
@@ -15494,27 +15437,27 @@
     <row r="132" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>5495</v>
-      </c>
-      <c r="B132" s="51" t="s">
-        <v>94</v>
+        <v>6866</v>
+      </c>
+      <c r="B132" s="132" t="s">
+        <v>92</v>
       </c>
       <c r="C132" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D132" s="133">
-        <v>1001093345495</v>
+        <v>22</v>
+      </c>
+      <c r="D132" s="50">
+        <v>1001095716866</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="125">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" ref="G132:G133" si="27">E132*F132</f>
+        <f>E132</f>
         <v>0</v>
       </c>
       <c r="H132" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I132" s="29">
         <v>60</v>
@@ -15581,30 +15524,30 @@
     <row r="133" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7377</v>
+        <v>5495</v>
       </c>
       <c r="B133" s="51" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C133" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="133">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="125">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G133:G134" si="27">E133*F133</f>
         <v>0</v>
       </c>
       <c r="H133" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I133" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J133" s="29"/>
       <c r="K133" s="27"/>
@@ -15665,33 +15608,33 @@
       <c r="BN133" s="100"/>
       <c r="BO133" s="100"/>
     </row>
-    <row r="134" spans="1:67" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6025</v>
+        <v>7377</v>
       </c>
       <c r="B134" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C134" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D134" s="133">
-        <v>1001094966025</v>
+        <v>1001095027377</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="125">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G134" s="23">
-        <f>E134</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H134" s="29">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="I134" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J134" s="29"/>
       <c r="K134" s="27"/>
@@ -15752,104 +15695,161 @@
       <c r="BN134" s="100"/>
       <c r="BO134" s="100"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" s="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>6929</v>
+        <v>6025</v>
       </c>
       <c r="B135" s="51" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="C135" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="133">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E135" s="24"/>
-      <c r="F135" s="125"/>
+      <c r="F135" s="125">
+        <v>3</v>
+      </c>
       <c r="G135" s="23">
         <f>E135</f>
         <v>0</v>
       </c>
-      <c r="H135" s="29"/>
-      <c r="I135" s="29"/>
-      <c r="J135" s="29" t="str">
-        <f>VLOOKUP(D135,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
+      <c r="H135" s="29">
+        <v>6</v>
+      </c>
+      <c r="I135" s="29">
+        <v>60</v>
+      </c>
+      <c r="J135" s="29"/>
+      <c r="K135" s="27"/>
       <c r="L135" s="100"/>
+      <c r="M135" s="100"/>
+      <c r="N135" s="100"/>
+      <c r="O135" s="100"/>
+      <c r="P135" s="100"/>
+      <c r="Q135" s="100"/>
+      <c r="R135" s="100"/>
+      <c r="S135" s="100"/>
+      <c r="T135" s="100"/>
+      <c r="U135" s="100"/>
+      <c r="V135" s="100"/>
+      <c r="W135" s="100"/>
+      <c r="X135" s="100"/>
+      <c r="Y135" s="100"/>
+      <c r="Z135" s="100"/>
+      <c r="AA135" s="100"/>
+      <c r="AB135" s="100"/>
+      <c r="AC135" s="100"/>
+      <c r="AD135" s="100"/>
+      <c r="AE135" s="100"/>
+      <c r="AF135" s="100"/>
+      <c r="AG135" s="100"/>
+      <c r="AH135" s="100"/>
+      <c r="AI135" s="100"/>
+      <c r="AJ135" s="100"/>
+      <c r="AK135" s="100"/>
+      <c r="AL135" s="100"/>
+      <c r="AM135" s="100"/>
+      <c r="AN135" s="100"/>
+      <c r="AO135" s="100"/>
+      <c r="AP135" s="100"/>
+      <c r="AQ135" s="100"/>
+      <c r="AR135" s="100"/>
+      <c r="AS135" s="100"/>
+      <c r="AT135" s="100"/>
+      <c r="AU135" s="100"/>
+      <c r="AV135" s="100"/>
+      <c r="AW135" s="100"/>
+      <c r="AX135" s="100"/>
+      <c r="AY135" s="100"/>
+      <c r="AZ135" s="100"/>
+      <c r="BA135" s="100"/>
+      <c r="BB135" s="100"/>
+      <c r="BC135" s="100"/>
+      <c r="BD135" s="100"/>
+      <c r="BE135" s="100"/>
+      <c r="BF135" s="100"/>
+      <c r="BG135" s="100"/>
+      <c r="BH135" s="100"/>
+      <c r="BI135" s="100"/>
+      <c r="BJ135" s="100"/>
+      <c r="BK135" s="100"/>
+      <c r="BL135" s="100"/>
+      <c r="BM135" s="100"/>
+      <c r="BN135" s="100"/>
+      <c r="BO135" s="100"/>
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7485</v>
+        <v>6929</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C136" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D136" s="133">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E136" s="24"/>
-      <c r="F136" s="125">
-        <v>0.15</v>
-      </c>
+      <c r="F136" s="125"/>
       <c r="G136" s="23">
-        <f>F136*E136</f>
+        <f>E136</f>
         <v>0</v>
       </c>
       <c r="H136" s="29"/>
       <c r="I136" s="29"/>
-      <c r="J136" s="29"/>
+      <c r="J136" s="29" t="str">
+        <f>VLOOKUP(D136,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
       <c r="L136" s="100"/>
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7730</v>
+        <v>7485</v>
       </c>
       <c r="B137" s="51" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C137" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="133">
-        <v>1001097747730</v>
+        <v>1001107397485</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="125">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
-        <f>E137*F137</f>
+        <f>F137*E137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29"/>
       <c r="I137" s="29"/>
-      <c r="J137" s="29" t="str">
-        <f>VLOOKUP(D137,[1]Бланк!$D:$J,7,0)</f>
-        <v>Ротация кода 7647</v>
-      </c>
+      <c r="J137" s="29"/>
       <c r="L137" s="100"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="134" t="str">
         <f t="shared" si="25"/>
-        <v>7731</v>
+        <v>7730</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C138" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="133">
-        <v>1001097767731</v>
+        <v>1001097747730</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="125">
@@ -15859,86 +15859,85 @@
         <f>E138*F138</f>
         <v>0</v>
       </c>
-      <c r="H138" s="29">
-        <v>1</v>
-      </c>
-      <c r="I138" s="29">
-        <v>30</v>
-      </c>
+      <c r="H138" s="29"/>
+      <c r="I138" s="29"/>
       <c r="J138" s="29" t="str">
         <f>VLOOKUP(D138,[1]Бланк!$D:$J,7,0)</f>
+        <v>Ротация кода 7647</v>
+      </c>
+      <c r="L138" s="100"/>
+    </row>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="134" t="str">
+        <f t="shared" si="25"/>
+        <v>7731</v>
+      </c>
+      <c r="B139" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="C139" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D139" s="133">
+        <v>1001097767731</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="125">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f>E139*F139</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="29">
+        <v>1</v>
+      </c>
+      <c r="I139" s="29">
+        <v>30</v>
+      </c>
+      <c r="J139" s="29" t="str">
+        <f>VLOOKUP(D139,[1]Бланк!$D:$J,7,0)</f>
         <v>Ротация кода 7651</v>
       </c>
-      <c r="L138" s="100"/>
-    </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
+      <c r="L139" s="100"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B139" s="42" t="s">
+      <c r="B140" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
-      <c r="L139" s="100"/>
-    </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="134" t="str">
-        <f t="shared" ref="A140:A152" si="28">RIGHT(D140,4)</f>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="42"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
+      <c r="L140" s="100"/>
+    </row>
+    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="134" t="str">
+        <f t="shared" ref="A141:A153" si="28">RIGHT(D141,4)</f>
         <v>7090</v>
       </c>
-      <c r="B140" s="35" t="s">
+      <c r="B141" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="C140" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D140" s="50">
-        <v>1001084217090</v>
-      </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G140" s="23">
-        <f t="shared" ref="G140:G141" si="29">E140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I140" s="14">
-        <v>50</v>
-      </c>
-      <c r="J140" s="29"/>
-      <c r="L140" s="100"/>
-    </row>
-    <row r="141" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="134" t="str">
-        <f t="shared" si="28"/>
-        <v>7187</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>101</v>
       </c>
       <c r="C141" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="50">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="23">
         <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G141:G142" si="29">E141*F141</f>
         <v>0</v>
       </c>
       <c r="H141" s="14">
@@ -15953,30 +15952,30 @@
     <row r="142" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6008</v>
+        <v>7187</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="C142" s="49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" s="50">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="23">
         <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H142" s="14">
         <v>1.8</v>
       </c>
       <c r="I142" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J142" s="29"/>
       <c r="L142" s="100"/>
@@ -15984,30 +15983,30 @@
     <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B143" s="35" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
       <c r="C143" s="49" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="50">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G143" s="23">
         <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I143" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J143" s="29"/>
       <c r="L143" s="100"/>
@@ -16015,30 +16014,30 @@
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7103</v>
+        <v>6620</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>199</v>
+        <v>97</v>
       </c>
       <c r="C144" s="49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D144" s="50">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" ref="G144:G151" si="30">E144*F144</f>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I144" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J144" s="29"/>
       <c r="L144" s="100"/>
@@ -16046,27 +16045,27 @@
     <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7092</v>
+        <v>7103</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="C145" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D145" s="50">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G145:G152" si="30">E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I145" s="14">
         <v>50</v>
@@ -16077,30 +16076,30 @@
     <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6228</v>
+        <v>7092</v>
       </c>
       <c r="B146" s="35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C146" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D146" s="50">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G146" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H146" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I146" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J146" s="29"/>
       <c r="L146" s="100"/>
@@ -16108,172 +16107,174 @@
     <row r="147" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6208</v>
+        <v>6228</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C147" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="50">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G147" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H147" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I147" s="14">
         <v>45</v>
       </c>
       <c r="J147" s="29"/>
-    </row>
-    <row r="148" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L147" s="100"/>
+    </row>
+    <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6754</v>
+        <v>6208</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="C148" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="50">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G148" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H148" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I148" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J148" s="29"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>6279</v>
+        <v>6754</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="C149" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="50">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I149" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J149" s="29"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7612</v>
+        <v>6279</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="C150" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D150" s="50">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G150" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H150" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I150" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J150" s="29"/>
     </row>
-    <row r="151" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7344</v>
+        <v>7612</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C151" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="50">
-        <v>1001122287344</v>
+        <v>1001453907612</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>0.33800000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="G151" s="23">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H151" s="14"/>
-      <c r="I151" s="14"/>
-      <c r="J151" s="29" t="str">
-        <f>VLOOKUP(D151,[1]Бланк!$D:$J,7,0)</f>
-        <v>Новинка</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H151" s="14">
+        <v>1</v>
+      </c>
+      <c r="I151" s="14">
+        <v>60</v>
+      </c>
+      <c r="J151" s="29"/>
+    </row>
+    <row r="152" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="134" t="str">
         <f t="shared" si="28"/>
-        <v>7345</v>
+        <v>7344</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C152" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="50">
-        <v>1001123677345</v>
+        <v>1001122287344</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.32500000000000001</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G152" s="23">
-        <f>E152*F152</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H152" s="14"/>
@@ -16283,37 +16284,56 @@
         <v>Новинка</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="48"/>
-      <c r="B153" s="45" t="s">
+    <row r="153" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="134" t="str">
+        <f t="shared" si="28"/>
+        <v>7345</v>
+      </c>
+      <c r="B153" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="C153" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="50">
+        <v>1001123677345</v>
+      </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="23">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G153" s="23">
+        <f>E153*F153</f>
+        <v>0</v>
+      </c>
+      <c r="H153" s="14"/>
+      <c r="I153" s="14"/>
+      <c r="J153" s="29" t="str">
+        <f>VLOOKUP(D153,[1]Бланк!$D:$J,7,0)</f>
+        <v>Новинка</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="48"/>
+      <c r="B154" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C153" s="16"/>
-      <c r="D153" s="36"/>
-      <c r="E153" s="17">
-        <f>SUM(E10:E150)</f>
+      <c r="C154" s="16"/>
+      <c r="D154" s="36"/>
+      <c r="E154" s="17">
+        <f>SUM(E10:E151)</f>
         <v>0</v>
       </c>
-      <c r="F153" s="17"/>
-      <c r="G153" s="17">
-        <f>SUM(G11:G152)</f>
+      <c r="F154" s="17"/>
+      <c r="G154" s="17">
+        <f>SUM(G11:G153)</f>
         <v>0</v>
       </c>
-      <c r="H153" s="17"/>
-      <c r="I153" s="17"/>
-      <c r="J153" s="17"/>
-    </row>
-    <row r="154" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="37"/>
-      <c r="C154" s="18"/>
-      <c r="D154" s="40"/>
-      <c r="F154" s="19"/>
-      <c r="G154" s="19"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="20"/>
-      <c r="J154" s="21"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H154" s="17"/>
+      <c r="I154" s="17"/>
+      <c r="J154" s="17"/>
+    </row>
+    <row r="155" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B155" s="37"/>
       <c r="C155" s="18"/>
       <c r="D155" s="40"/>
@@ -16325,13 +16345,12 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B156" s="37"/>
-      <c r="C156" s="53"/>
-      <c r="D156" s="54"/>
-      <c r="E156" s="55"/>
-      <c r="F156" s="56"/>
-      <c r="G156" s="56"/>
-      <c r="H156" s="57"/>
-      <c r="I156" s="57"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="40"/>
+      <c r="F156" s="19"/>
+      <c r="G156" s="19"/>
+      <c r="H156" s="20"/>
+      <c r="I156" s="20"/>
       <c r="J156" s="21"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -16348,22 +16367,23 @@
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B158" s="37"/>
       <c r="C158" s="53"/>
-      <c r="D158" s="58"/>
-      <c r="E158" s="59"/>
-      <c r="F158" s="58"/>
-      <c r="G158" s="60"/>
-      <c r="H158" s="61"/>
-      <c r="I158" s="62"/>
+      <c r="D158" s="54"/>
+      <c r="E158" s="55"/>
+      <c r="F158" s="56"/>
+      <c r="G158" s="56"/>
+      <c r="H158" s="57"/>
+      <c r="I158" s="57"/>
       <c r="J158" s="21"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B159" s="37"/>
-      <c r="C159" s="18"/>
-      <c r="D159" s="40"/>
-      <c r="F159" s="19"/>
-      <c r="G159" s="19"/>
-      <c r="H159" s="20"/>
-      <c r="I159" s="20"/>
+      <c r="C159" s="53"/>
+      <c r="D159" s="58"/>
+      <c r="E159" s="59"/>
+      <c r="F159" s="58"/>
+      <c r="G159" s="60"/>
+      <c r="H159" s="61"/>
+      <c r="I159" s="62"/>
       <c r="J159" s="21"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -31506,13 +31526,23 @@
       <c r="I1673" s="20"/>
       <c r="J1673" s="21"/>
     </row>
+    <row r="1674" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1674" s="37"/>
+      <c r="C1674" s="18"/>
+      <c r="D1674" s="40"/>
+      <c r="F1674" s="19"/>
+      <c r="G1674" s="19"/>
+      <c r="H1674" s="20"/>
+      <c r="I1674" s="20"/>
+      <c r="J1674" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J154" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D158">
+  <conditionalFormatting sqref="D159">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -31524,7 +31554,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D158">
+  <conditionalFormatting sqref="D159">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06173D8B-5CD9-41F1-8D19-C9C84B6D2F20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7EE8F-E994-4CF8-A734-D54FE77BAECC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,9 +919,6 @@
     <t xml:space="preserve">ЛП Луганск </t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
     <t>Грация</t>
   </si>
   <si>
@@ -1007,6 +1004,9 @@
   </si>
   <si>
     <t>САЛЯМИ ZHAZIRA ASLAM в/к в/у 0.82кг</t>
+  </si>
+  <si>
+    <t>ЛП Луганск (АСЛАМ)</t>
   </si>
 </sst>
 </file>
@@ -9238,6 +9238,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="124">
+        <f>K2</f>
         <v>130438644</v>
       </c>
       <c r="E1" s="135" t="s">
@@ -9278,8 +9279,9 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="138" t="s">
-        <v>194</v>
+      <c r="G3" s="138" t="str">
+        <f>VLOOKUP(D1,K:L,2,0)</f>
+        <v>ЛП Луганск - 130438644</v>
       </c>
       <c r="H3" s="136"/>
       <c r="I3" s="136"/>
@@ -9299,7 +9301,7 @@
         <v>187</v>
       </c>
       <c r="O4" s="97" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
@@ -9312,9 +9314,11 @@
       <c r="G5" s="8"/>
       <c r="H5" s="22"/>
       <c r="I5" s="22"/>
-      <c r="K5" s="27" t="str">
-        <f t="shared" ref="K5:K7" si="0">LEFT(L5,9)</f>
-        <v/>
+      <c r="K5" s="122">
+        <v>130439452</v>
+      </c>
+      <c r="L5" s="100" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9327,7 +9331,7 @@
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
       <c r="K6" s="27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K5:K7" si="0">LEFT(L6,9)</f>
         <v/>
       </c>
     </row>
@@ -9809,7 +9813,7 @@
         <v>7754</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>22</v>
@@ -10383,7 +10387,7 @@
         <v>8014</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C27" s="49" t="s">
         <v>22</v>
@@ -10470,7 +10474,7 @@
         <v>7514</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C28" s="49" t="s">
         <v>22</v>
@@ -10554,7 +10558,7 @@
         <v>7518</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>22</v>
@@ -11003,7 +11007,7 @@
         <v>7601</v>
       </c>
       <c r="B35" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="49" t="s">
         <v>20</v>
@@ -11177,7 +11181,7 @@
         <v>7040</v>
       </c>
       <c r="B37" s="51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C37" s="49" t="s">
         <v>20</v>
@@ -12894,7 +12898,7 @@
         <v>7490</v>
       </c>
       <c r="B60" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C60" s="49" t="s">
         <v>20</v>
@@ -13330,7 +13334,7 @@
         <v>7399</v>
       </c>
       <c r="B75" s="51" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C75" s="49" t="s">
         <v>20</v>
@@ -13388,7 +13392,7 @@
         <v>7233</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C77" s="49" t="s">
         <v>20</v>
@@ -13630,7 +13634,7 @@
         <v>7562</v>
       </c>
       <c r="B85" s="51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C85" s="49" t="s">
         <v>22</v>
@@ -13782,7 +13786,7 @@
         <v>7156</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C90" s="49" t="s">
         <v>20</v>
@@ -13905,7 +13909,7 @@
         <v>7516</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C94" s="49" t="s">
         <v>20</v>
@@ -13935,7 +13939,7 @@
         <v>7710</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C95" s="49" t="s">
         <v>20</v>
@@ -13965,7 +13969,7 @@
         <v>7513</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C96" s="49" t="s">
         <v>20</v>
@@ -14026,7 +14030,7 @@
         <v>7608</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C98" s="49" t="s">
         <v>20</v>
@@ -14192,7 +14196,7 @@
         <v>7700</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="49" t="s">
         <v>22</v>
@@ -14747,7 +14751,7 @@
         <v>7613</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C120" s="49" t="s">
         <v>20</v>
@@ -15093,7 +15097,7 @@
         <v>4584</v>
       </c>
       <c r="B128" s="96" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C128" s="49" t="s">
         <v>22</v>
@@ -15180,7 +15184,7 @@
         <v>7725</v>
       </c>
       <c r="B129" s="96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C129" s="49" t="s">
         <v>20</v>
@@ -15353,7 +15357,7 @@
         <v>3215</v>
       </c>
       <c r="B131" s="132" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C131" s="49" t="s">
         <v>20</v>
@@ -15788,7 +15792,7 @@
         <v>6929</v>
       </c>
       <c r="B136" s="51" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C136" s="49" t="s">
         <v>22</v>
@@ -15816,7 +15820,7 @@
         <v>7485</v>
       </c>
       <c r="B137" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C137" s="49" t="s">
         <v>20</v>
@@ -15843,7 +15847,7 @@
         <v>7730</v>
       </c>
       <c r="B138" s="51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C138" s="49" t="s">
         <v>20</v>
@@ -15873,7 +15877,7 @@
         <v>7731</v>
       </c>
       <c r="B139" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C139" s="49" t="s">
         <v>20</v>
@@ -16048,7 +16052,7 @@
         <v>7103</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C145" s="49" t="s">
         <v>20</v>
@@ -16171,7 +16175,7 @@
         <v>6754</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C149" s="49" t="s">
         <v>20</v>
@@ -16261,7 +16265,7 @@
         <v>7344</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C152" s="49" t="s">
         <v>20</v>
@@ -16290,7 +16294,7 @@
         <v>7345</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C153" s="49" t="s">
         <v>20</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E7EE8F-E994-4CF8-A734-D54FE77BAECC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4C16D2-0D40-4C3B-9F33-7D76CFBC9AF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9331,7 +9331,7 @@
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
       <c r="K6" s="27" t="str">
-        <f t="shared" ref="K5:K7" si="0">LEFT(L6,9)</f>
+        <f t="shared" ref="K6:K7" si="0">LEFT(L6,9)</f>
         <v/>
       </c>
     </row>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4C16D2-0D40-4C3B-9F33-7D76CFBC9AF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEC761B-B199-44DB-8B4E-1E17B0FC85E7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1007,6 +1007,9 @@
   </si>
   <si>
     <t>ЛП Луганск (АСЛАМ)</t>
+  </si>
+  <si>
+    <t>РУБЛЕНЫЕ сос ц/о в/у 0.36кг 8шт.</t>
   </si>
 </sst>
 </file>
@@ -12305,16 +12308,16 @@
     <row r="50" spans="1:67" s="52" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="134" t="str">
         <f t="shared" si="1"/>
-        <v>6765</v>
+        <v>7520</v>
       </c>
       <c r="B50" s="51" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="C50" s="49" t="s">
         <v>20</v>
       </c>
       <c r="D50" s="50">
-        <v>1001023696765</v>
+        <v>1001023697520</v>
       </c>
       <c r="E50" s="24"/>
       <c r="F50" s="125">
@@ -12324,12 +12327,8 @@
         <f>E50*F50</f>
         <v>0</v>
       </c>
-      <c r="H50" s="29">
-        <v>2.16</v>
-      </c>
-      <c r="I50" s="29">
-        <v>45</v>
-      </c>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
       <c r="J50" s="29"/>
       <c r="K50" s="27"/>
       <c r="L50" s="100"/>
